--- a/weeks/undefined_20260929.xlsx
+++ b/weeks/undefined_20260929.xlsx
@@ -487,6 +487,9 @@
     <xf numFmtId="164" fontId="25" fillId="8" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="7" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
@@ -500,9 +503,6 @@
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="30" fillId="6" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="6" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="24" fillId="8" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
@@ -616,13 +616,13 @@
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="n">
-        <v>0.0</v>
+        <v>2.72</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>0.0</v>
+        <v>3.92</v>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="H3" s="37" t="n">
-        <v>0.0</v>
+        <v>3.92</v>
       </c>
       <c r="I3" s="18" t="n">
         <v>0.0</v>
       </c>
       <c r="J3" s="38" t="n">
-        <v>0.0</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="4" customHeight="true" ht="21.75">
@@ -652,13 +652,13 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="21" t="n">
-        <v>0.0</v>
+        <v>2.72</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>0.0</v>
+        <v>3.92</v>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="H4" s="39" t="n">
-        <v>0.0</v>
+        <v>3.92</v>
       </c>
       <c r="I4" s="25" t="n">
         <v>0.0</v>
       </c>
       <c r="J4" s="40" t="n">
-        <v>0.0</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="5" customHeight="true" ht="21.75">
@@ -688,27 +688,27 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>0.0</v>
+        <v>2.72</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>0.0</v>
+        <v>2.72</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>0.0</v>
+        <v>3.92</v>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="30" t="n">
-        <v>0.0</v>
+      <c r="H5" s="41" t="n">
+        <v>3.92</v>
       </c>
       <c r="I5" s="31" t="n">
         <v>0.0</v>
       </c>
-      <c r="J5" s="31" t="n">
-        <v>0.0</v>
+      <c r="J5" s="42" t="n">
+        <v>3.92</v>
       </c>
     </row>
     <row r="6" customHeight="true" ht="21.75">
@@ -746,27 +746,27 @@
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="14" t="n">
-        <v>36.33</v>
+        <v>23.48</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>33.97</v>
+        <v>20.05</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="H7" s="37" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="I7" s="38" t="n">
-        <v>30.21</v>
+        <v>-0.75</v>
+      </c>
+      <c r="I7" s="43" t="n">
+        <v>19.2</v>
       </c>
       <c r="J7" s="38" t="n">
-        <v>3.76</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="21.75">
@@ -782,27 +782,27 @@
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="21" t="n">
-        <v>9.85</v>
+        <v>11.8</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>9.76</v>
+        <v>8.73</v>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="H8" s="39" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I8" s="40" t="n">
-        <v>8.91</v>
+        <v>0.13</v>
+      </c>
+      <c r="I8" s="44" t="n">
+        <v>8.1</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="9" customHeight="true" ht="21.75">
@@ -818,27 +818,27 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>9.85</v>
+        <v>11.8</v>
       </c>
       <c r="E9" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>9.76</v>
+        <v>8.73</v>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="H9" s="41" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>8.91</v>
+        <v>0.13</v>
+      </c>
+      <c r="I9" s="45" t="n">
+        <v>8.1</v>
       </c>
       <c r="J9" s="42" t="n">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="10" customHeight="true" ht="21.75">
@@ -854,27 +854,27 @@
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="21" t="n">
-        <v>9.48</v>
+        <v>8.69</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>8.72</v>
+        <v>8.45</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="H10" s="39" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I10" s="43" t="n">
-        <v>9.1</v>
+        <v>0.35</v>
+      </c>
+      <c r="I10" s="44" t="n">
+        <v>8.1</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>-0.38</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="11" customHeight="true" ht="21.75">
@@ -890,27 +890,27 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>9.48</v>
+        <v>8.69</v>
       </c>
       <c r="E11" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>8.72</v>
+        <v>8.45</v>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="H11" s="41" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I11" s="44" t="n">
-        <v>9.1</v>
+        <v>0.35</v>
+      </c>
+      <c r="I11" s="45" t="n">
+        <v>8.1</v>
       </c>
       <c r="J11" s="42" t="n">
-        <v>-0.38</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="12" customHeight="true" ht="21.75">
@@ -926,27 +926,27 @@
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" t="n">
-        <v>16.4</v>
+        <v>2.39</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>14.33</v>
+        <v>2.64</v>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="H12" s="39" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="I12" s="40" t="n">
-        <v>11.88</v>
+        <v>-1.26</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>3.0</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>2.45</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="13" customHeight="true" ht="21.75">
@@ -962,27 +962,27 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>16.4</v>
+        <v>2.39</v>
       </c>
       <c r="E13" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F13" s="28" t="n">
-        <v>14.33</v>
+        <v>2.64</v>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="H13" s="41" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>11.88</v>
+        <v>-1.26</v>
+      </c>
+      <c r="I13" s="31" t="n">
+        <v>3.0</v>
       </c>
       <c r="J13" s="42" t="n">
-        <v>2.45</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="14" customHeight="true" ht="21.75">
@@ -1004,21 +1004,21 @@
         <v>0.0</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>1.16</v>
+        <v>0.23</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H14" s="39" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I14" s="40" t="n">
-        <v>0.32</v>
+        <v>0.03</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>0.0</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>0.84</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="15" customHeight="true" ht="21.75">
@@ -1040,21 +1040,21 @@
         <v>0.0</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>1.16</v>
+        <v>0.23</v>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H15" s="41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>0.32</v>
+        <v>0.03</v>
+      </c>
+      <c r="I15" s="31" t="n">
+        <v>0.0</v>
       </c>
       <c r="J15" s="42" t="n">
-        <v>0.84</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="16" customHeight="true" ht="21.75">
@@ -1066,27 +1066,27 @@
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="14" t="n">
-        <v>3.47</v>
+        <v>8.33</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>6.54</v>
+        <v>6.47</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="H16" s="37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I16" s="38" t="n">
-        <v>6.39</v>
+        <v>0.87</v>
+      </c>
+      <c r="I16" s="43" t="n">
+        <v>5.4</v>
       </c>
       <c r="J16" s="38" t="n">
-        <v>0.15</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="17" customHeight="true" ht="21.75">
@@ -1102,27 +1102,27 @@
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" t="n">
-        <v>0.0</v>
+        <v>2.15</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="H17" s="39" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I17" s="43" t="n">
-        <v>1.5</v>
+        <v>0.74</v>
+      </c>
+      <c r="I17" s="44" t="n">
+        <v>1.4</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>0.52</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="18" customHeight="true" ht="21.75">
@@ -1138,27 +1138,27 @@
         </is>
       </c>
       <c r="D18" s="32" t="n">
-        <v>0.0</v>
+        <v>2.15</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="H18" s="45" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I18" s="46" t="n">
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="H18" s="46" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I18" s="47" t="n">
         <v>1.2</v>
       </c>
-      <c r="J18" s="47" t="n">
-        <v>0.51</v>
+      <c r="J18" s="48" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="19" customHeight="true" ht="21.75">
@@ -1180,21 +1180,21 @@
         <v>0.0</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="41" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I19" s="44" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
+      </c>
+      <c r="I19" s="45" t="n">
+        <v>0.2</v>
       </c>
       <c r="J19" s="42" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="20" customHeight="true" ht="21.75">
@@ -1210,27 +1210,27 @@
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" t="n">
-        <v>1.86</v>
+        <v>4.88</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="H20" s="39" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="I20" s="40" t="n">
-        <v>3.74</v>
+        <v>0.34</v>
+      </c>
+      <c r="I20" s="44" t="n">
+        <v>3.1</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>-0.48</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="21" customHeight="true" ht="21.75">
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="D21" s="27" t="n">
-        <v>0.57</v>
+        <v>4.36</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="H21" s="41" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I21" s="42" t="n">
-        <v>2.44</v>
+        <v>0.34</v>
+      </c>
+      <c r="I21" s="45" t="n">
+        <v>1.7</v>
       </c>
       <c r="J21" s="42" t="n">
-        <v>-0.22</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="22" customHeight="true" ht="21.75">
@@ -1282,27 +1282,27 @@
         </is>
       </c>
       <c r="D22" s="32" t="n">
-        <v>1.29</v>
+        <v>0.52</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F22" s="33" t="n">
-        <v>1.04</v>
+        <v>0.9</v>
       </c>
       <c r="G22" s="34" t="inlineStr">
         <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="H22" s="45" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="I22" s="46" t="n">
-        <v>1.3</v>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="47" t="n">
+        <v>1.4</v>
       </c>
       <c r="J22" s="47" t="n">
-        <v>-0.26</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="23" customHeight="true" ht="21.75">
@@ -1318,27 +1318,27 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="H23" s="39" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I23" s="40" t="n">
-        <v>1.15</v>
+        <v>-0.21</v>
+      </c>
+      <c r="I23" s="44" t="n">
+        <v>0.9</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="21.75">
@@ -1354,27 +1354,27 @@
         </is>
       </c>
       <c r="D24" s="32" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="G24" s="34" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="H24" s="45" t="n">
-        <v>0.06</v>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="H24" s="46" t="n">
+        <v>-0.21</v>
       </c>
       <c r="I24" s="47" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J24" s="47" t="n">
-        <v>0.11</v>
+        <v>0.9</v>
+      </c>
+      <c r="J24" s="48" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="25" customHeight="true" ht="21.75">
@@ -1386,27 +1386,27 @@
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="14" t="n">
-        <v>7.42</v>
+        <v>6.46</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>7.09</v>
+        <v>7.31</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="H25" s="37" t="n">
-        <v>-0.81</v>
-      </c>
-      <c r="I25" s="38" t="n">
-        <v>8.43</v>
+        <v>-0.09</v>
+      </c>
+      <c r="I25" s="43" t="n">
+        <v>7.7</v>
       </c>
       <c r="J25" s="38" t="n">
-        <v>-1.34</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="21.75">
@@ -1422,27 +1422,27 @@
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" t="n">
-        <v>5.68</v>
+        <v>4.82</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>5.57</v>
+        <v>5.56</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="H26" s="39" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="I26" s="40" t="n">
-        <v>6.71</v>
+        <v>-0.14</v>
+      </c>
+      <c r="I26" s="44" t="n">
+        <v>5.8</v>
       </c>
       <c r="J26" s="40" t="n">
-        <v>-1.14</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="27" customHeight="true" ht="21.75">
@@ -1458,27 +1458,27 @@
         </is>
       </c>
       <c r="D27" s="27" t="n">
-        <v>5.68</v>
+        <v>4.82</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>5.57</v>
+        <v>5.56</v>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="H27" s="41" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="I27" s="42" t="n">
-        <v>6.71</v>
+        <v>-0.14</v>
+      </c>
+      <c r="I27" s="45" t="n">
+        <v>5.8</v>
       </c>
       <c r="J27" s="42" t="n">
-        <v>-1.14</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="28" customHeight="true" ht="21.75">
@@ -1494,27 +1494,27 @@
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="H28" s="39" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="I28" s="40" t="n">
-        <v>1.72</v>
+        <v>0.05</v>
+      </c>
+      <c r="I28" s="44" t="n">
+        <v>1.9</v>
       </c>
       <c r="J28" s="40" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="29" customHeight="true" ht="21.75">
@@ -1530,27 +1530,27 @@
         </is>
       </c>
       <c r="D29" s="27" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="E29" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F29" s="28" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="H29" s="41" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="I29" s="42" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="J29" s="44" t="n">
-        <v>-0.2</v>
+        <v>0.05</v>
+      </c>
+      <c r="I29" s="45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J29" s="42" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="30" customHeight="true" ht="21.75">
@@ -1562,27 +1562,27 @@
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="14" t="n">
-        <v>13.86</v>
+        <v>11.41</v>
       </c>
       <c r="E30" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>13.82</v>
+        <v>13.06</v>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="H30" s="37" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="I30" s="38" t="n">
-        <v>15.82</v>
+        <v>-3.34</v>
+      </c>
+      <c r="I30" s="43" t="n">
+        <v>17.2</v>
       </c>
       <c r="J30" s="38" t="n">
-        <v>-2.0</v>
+        <v>-4.14</v>
       </c>
     </row>
     <row r="31" customHeight="true" ht="21.75">
@@ -1598,27 +1598,27 @@
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" t="n">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>2.18</v>
+        <v>3.18</v>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" s="39" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="I31" s="40" t="n">
-        <v>2.97</v>
+        <v>0.18</v>
+      </c>
+      <c r="I31" s="44" t="n">
+        <v>3.3</v>
       </c>
       <c r="J31" s="40" t="n">
-        <v>-0.79</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="32" customHeight="true" ht="21.75">
@@ -1634,27 +1634,27 @@
         </is>
       </c>
       <c r="D32" s="32" t="n">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F32" s="33" t="n">
-        <v>2.18</v>
+        <v>3.18</v>
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="H32" s="45" t="n">
-        <v>-0.92</v>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H32" s="46" t="n">
+        <v>0.18</v>
       </c>
       <c r="I32" s="47" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="J32" s="47" t="n">
-        <v>-0.79</v>
+        <v>3.3</v>
+      </c>
+      <c r="J32" s="48" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="33" customHeight="true" ht="21.75">
@@ -1670,27 +1670,27 @@
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" t="n">
-        <v>4.24</v>
+        <v>4.57</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>3.12</v>
+        <v>5.89</v>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="H33" s="39" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="I33" s="40" t="n">
-        <v>4.78</v>
+        <v>-1.91</v>
+      </c>
+      <c r="I33" s="44" t="n">
+        <v>8.1</v>
       </c>
       <c r="J33" s="40" t="n">
-        <v>-1.66</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="34" customHeight="true" ht="21.75">
@@ -1706,27 +1706,27 @@
         </is>
       </c>
       <c r="D34" s="32" t="n">
-        <v>4.24</v>
+        <v>4.57</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F34" s="33" t="n">
-        <v>3.12</v>
+        <v>5.89</v>
       </c>
       <c r="G34" s="34" t="inlineStr">
         <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="H34" s="45" t="n">
-        <v>-1.78</v>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="H34" s="46" t="n">
+        <v>-1.91</v>
       </c>
       <c r="I34" s="47" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="J34" s="47" t="n">
-        <v>-1.66</v>
+        <v>8.1</v>
+      </c>
+      <c r="J34" s="48" t="n">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="35" customHeight="true" ht="21.75">
@@ -1742,27 +1742,27 @@
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" t="n">
-        <v>9.3</v>
+        <v>5.89</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>8.52</v>
+        <v>3.99</v>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="H35" s="39" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I35" s="40" t="n">
-        <v>8.07</v>
+        <v>-1.61</v>
+      </c>
+      <c r="I35" s="44" t="n">
+        <v>5.8</v>
       </c>
       <c r="J35" s="40" t="n">
-        <v>0.45</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="36" customHeight="true" ht="21.75">
@@ -1778,27 +1778,27 @@
         </is>
       </c>
       <c r="D36" s="32" t="n">
-        <v>9.3</v>
+        <v>5.89</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F36" s="33" t="n">
-        <v>8.52</v>
+        <v>3.99</v>
       </c>
       <c r="G36" s="34" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H36" s="45" t="n">
-        <v>0.52</v>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="H36" s="46" t="n">
+        <v>-1.61</v>
       </c>
       <c r="I36" s="47" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="J36" s="47" t="n">
-        <v>0.45</v>
+        <v>5.8</v>
+      </c>
+      <c r="J36" s="48" t="n">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="37" customHeight="true" ht="21.75">
@@ -1810,27 +1810,27 @@
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="14" t="n">
-        <v>13.53</v>
+        <v>15.86</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>13.68</v>
+        <v>14.06</v>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="H37" s="37" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="I37" s="38" t="n">
-        <v>14.89</v>
+        <v>-0.44</v>
+      </c>
+      <c r="I37" s="43" t="n">
+        <v>14.2</v>
       </c>
       <c r="J37" s="38" t="n">
-        <v>-1.21</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="38" customHeight="true" ht="21.75">
@@ -1846,27 +1846,27 @@
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" t="n">
-        <v>3.56</v>
+        <v>3.32</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>3.68</v>
+        <v>3.23</v>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="H38" s="39" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="I38" s="40" t="n">
-        <v>3.66</v>
+        <v>-0.47</v>
+      </c>
+      <c r="I38" s="44" t="n">
+        <v>3.2</v>
       </c>
       <c r="J38" s="40" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="39" customHeight="true" ht="21.75">
@@ -1882,27 +1882,27 @@
         </is>
       </c>
       <c r="D39" s="27" t="n">
-        <v>3.56</v>
+        <v>3.32</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>3.68</v>
+        <v>3.23</v>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="H39" s="41" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="I39" s="42" t="n">
-        <v>3.66</v>
+        <v>-0.47</v>
+      </c>
+      <c r="I39" s="45" t="n">
+        <v>3.2</v>
       </c>
       <c r="J39" s="42" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="40" customHeight="true" ht="21.75">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" t="n">
-        <v>5.39</v>
+        <v>5.27</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>4.99</v>
+        <v>5.3</v>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H40" s="39" t="n">
-        <v>-0.81</v>
-      </c>
-      <c r="I40" s="40" t="n">
-        <v>6.57</v>
+        <v>0.3</v>
+      </c>
+      <c r="I40" s="44" t="n">
+        <v>5.3</v>
       </c>
       <c r="J40" s="40" t="n">
-        <v>-1.58</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41" customHeight="true" ht="21.75">
@@ -1954,27 +1954,27 @@
         </is>
       </c>
       <c r="D41" s="27" t="n">
-        <v>5.39</v>
+        <v>5.27</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>4.99</v>
+        <v>5.3</v>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="H41" s="41" t="n">
-        <v>-0.81</v>
-      </c>
-      <c r="I41" s="42" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="J41" s="42" t="n">
-        <v>-1.58</v>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H41" s="49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I41" s="45" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J41" s="31" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="42" customHeight="true" ht="21.75">
@@ -1990,27 +1990,27 @@
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="21" t="n">
-        <v>4.58</v>
+        <v>7.27</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>5.01</v>
+        <v>5.53</v>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="H42" s="39" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I42" s="40" t="n">
-        <v>4.66</v>
+        <v>-0.27</v>
+      </c>
+      <c r="I42" s="44" t="n">
+        <v>5.7</v>
       </c>
       <c r="J42" s="40" t="n">
-        <v>0.35</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="43" customHeight="true" ht="21.75">
@@ -2026,27 +2026,27 @@
         </is>
       </c>
       <c r="D43" s="27" t="n">
-        <v>4.58</v>
+        <v>7.27</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5.01</v>
+        <v>5.53</v>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="H43" s="41" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I43" s="42" t="n">
-        <v>4.66</v>
+        <v>-0.27</v>
+      </c>
+      <c r="I43" s="45" t="n">
+        <v>5.7</v>
       </c>
       <c r="J43" s="42" t="n">
-        <v>0.35</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="44" customHeight="true" ht="21.75">
@@ -2058,27 +2058,27 @@
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="14" t="n">
-        <v>12.42</v>
+        <v>14.45</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>12.37</v>
+        <v>16.21</v>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="H44" s="37" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I44" s="38" t="n">
-        <v>10.81</v>
+        <v>1.51</v>
+      </c>
+      <c r="I44" s="43" t="n">
+        <v>14.9</v>
       </c>
       <c r="J44" s="38" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="45" customHeight="true" ht="21.75">
@@ -2094,27 +2094,27 @@
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="21" t="n">
-        <v>3.53</v>
+        <v>5.98</v>
       </c>
       <c r="E45" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>5.43</v>
+        <v>6.32</v>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H45" s="39" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I45" s="40" t="n">
-        <v>4.41</v>
+        <v>0.82</v>
+      </c>
+      <c r="I45" s="44" t="n">
+        <v>5.1</v>
       </c>
       <c r="J45" s="40" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="46" customHeight="true" ht="21.75">
@@ -2130,27 +2130,27 @@
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>3.53</v>
+        <v>5.98</v>
       </c>
       <c r="E46" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F46" s="33" t="n">
-        <v>5.43</v>
+        <v>6.32</v>
       </c>
       <c r="G46" s="34" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="H46" s="45" t="n">
-        <v>0.23</v>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H46" s="46" t="n">
+        <v>0.82</v>
       </c>
       <c r="I46" s="47" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="J46" s="47" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
+      </c>
+      <c r="J46" s="48" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="47" customHeight="true" ht="21.75">
@@ -2166,27 +2166,27 @@
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="21" t="n">
-        <v>6.74</v>
+        <v>4.98</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>5.36</v>
+        <v>6.31</v>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="H47" s="39" t="n">
-        <v>0.56</v>
-      </c>
-      <c r="I47" s="40" t="n">
-        <v>4.56</v>
+        <v>1.61</v>
+      </c>
+      <c r="I47" s="44" t="n">
+        <v>4.9</v>
       </c>
       <c r="J47" s="40" t="n">
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="48" customHeight="true" ht="21.75">
@@ -2202,27 +2202,27 @@
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="E48" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F48" s="33" t="n">
-        <v>3.39</v>
+        <v>3.56</v>
       </c>
       <c r="G48" s="34" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="H48" s="45" t="n">
-        <v>-1.41</v>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="H48" s="46" t="n">
+        <v>-1.14</v>
       </c>
       <c r="I48" s="47" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="J48" s="47" t="n">
-        <v>-1.17</v>
+        <v>4.9</v>
+      </c>
+      <c r="J48" s="48" t="n">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="49" customHeight="true" ht="21.75">
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="D49" s="27" t="n">
-        <v>2.54</v>
+        <v>1.18</v>
       </c>
       <c r="E49" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="H49" s="41" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="I49" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J49" s="42" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="50" customHeight="true" ht="21.75">
@@ -2274,27 +2274,27 @@
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="21" t="n">
-        <v>2.15</v>
+        <v>3.49</v>
       </c>
       <c r="E50" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>1.58</v>
+        <v>3.58</v>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H50" s="39" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="I50" s="40" t="n">
-        <v>1.84</v>
+        <v>-0.92</v>
+      </c>
+      <c r="I50" s="44" t="n">
+        <v>4.9</v>
       </c>
       <c r="J50" s="40" t="n">
-        <v>-0.26</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="51" customHeight="true" ht="21.75">
@@ -2310,27 +2310,27 @@
         </is>
       </c>
       <c r="D51" s="27" t="n">
-        <v>2.15</v>
+        <v>3.49</v>
       </c>
       <c r="E51" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F51" s="28" t="n">
-        <v>1.58</v>
+        <v>3.58</v>
       </c>
       <c r="G51" s="29" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H51" s="41" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="I51" s="42" t="n">
-        <v>1.84</v>
+        <v>-0.92</v>
+      </c>
+      <c r="I51" s="45" t="n">
+        <v>4.9</v>
       </c>
       <c r="J51" s="42" t="n">
-        <v>-0.26</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="52" customHeight="true" ht="21.75">
@@ -2342,27 +2342,27 @@
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="14" t="n">
-        <v>9.54</v>
+        <v>15.02</v>
       </c>
       <c r="E52" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>10.33</v>
+        <v>16.19</v>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="H52" s="37" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="I52" s="38" t="n">
-        <v>12.58</v>
+        <v>-2.91</v>
+      </c>
+      <c r="I52" s="43" t="n">
+        <v>20.3</v>
       </c>
       <c r="J52" s="38" t="n">
-        <v>-2.25</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="53" customHeight="true" ht="21.75">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="21" t="n">
-        <v>1.48</v>
+        <v>3.37</v>
       </c>
       <c r="E53" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>2.41</v>
+        <v>3.18</v>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="H53" s="39" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="I53" s="40" t="n">
-        <v>2.32</v>
+        <v>-1.22</v>
+      </c>
+      <c r="I53" s="44" t="n">
+        <v>4.7</v>
       </c>
       <c r="J53" s="40" t="n">
-        <v>0.09</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="21.75">
@@ -2414,27 +2414,27 @@
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>1.48</v>
+        <v>3.37</v>
       </c>
       <c r="E54" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F54" s="33" t="n">
-        <v>2.41</v>
+        <v>3.18</v>
       </c>
       <c r="G54" s="34" t="inlineStr">
         <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="H54" s="45" t="n">
-        <v>-0.29</v>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H54" s="46" t="n">
+        <v>-1.22</v>
       </c>
       <c r="I54" s="47" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J54" s="47" t="n">
-        <v>0.09</v>
+        <v>4.7</v>
+      </c>
+      <c r="J54" s="48" t="n">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="55" customHeight="true" ht="21.75">
@@ -2450,27 +2450,27 @@
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="21" t="n">
-        <v>4.94</v>
+        <v>5.93</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>4.91</v>
+        <v>6.95</v>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="H55" s="39" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="I55" s="40" t="n">
-        <v>5.82</v>
+        <v>-0.45</v>
+      </c>
+      <c r="I55" s="44" t="n">
+        <v>7.7</v>
       </c>
       <c r="J55" s="40" t="n">
-        <v>-0.91</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="56" customHeight="true" ht="21.75">
@@ -2486,27 +2486,27 @@
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>4.28</v>
+        <v>4.99</v>
       </c>
       <c r="E56" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F56" s="33" t="n">
-        <v>4.42</v>
+        <v>6.11</v>
       </c>
       <c r="G56" s="34" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H56" s="45" t="n">
-        <v>-1.58</v>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="H56" s="46" t="n">
+        <v>-1.29</v>
       </c>
       <c r="I56" s="47" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="J56" s="46" t="n">
-        <v>-1.4</v>
+        <v>7.7</v>
+      </c>
+      <c r="J56" s="48" t="n">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="57" customHeight="true" ht="21.75">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="D57" s="27" t="n">
-        <v>0.66</v>
+        <v>0.94</v>
       </c>
       <c r="E57" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F57" s="28" t="n">
-        <v>0.49</v>
+        <v>0.84</v>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
@@ -2536,13 +2536,13 @@
         </is>
       </c>
       <c r="H57" s="41" t="n">
-        <v>0.49</v>
+        <v>0.84</v>
       </c>
       <c r="I57" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J57" s="42" t="n">
-        <v>0.49</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="58" customHeight="true" ht="21.75">
@@ -2558,27 +2558,27 @@
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="21" t="n">
-        <v>1.32</v>
+        <v>2.77</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F58" s="22" t="n">
-        <v>1.58</v>
+        <v>3.19</v>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H58" s="39" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="I58" s="40" t="n">
-        <v>2.86</v>
+        <v>-0.81</v>
+      </c>
+      <c r="I58" s="44" t="n">
+        <v>4.3</v>
       </c>
       <c r="J58" s="40" t="n">
-        <v>-1.28</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="59" customHeight="true" ht="21.75">
@@ -2594,27 +2594,27 @@
         </is>
       </c>
       <c r="D59" s="27" t="n">
-        <v>1.32</v>
+        <v>2.77</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>1.58</v>
+        <v>3.19</v>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H59" s="41" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="I59" s="42" t="n">
-        <v>2.86</v>
+        <v>-0.81</v>
+      </c>
+      <c r="I59" s="45" t="n">
+        <v>4.3</v>
       </c>
       <c r="J59" s="42" t="n">
-        <v>-1.28</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="21.75">
@@ -2630,27 +2630,27 @@
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="21" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="E60" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>1.43</v>
+        <v>2.87</v>
       </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="H60" s="39" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="I60" s="40" t="n">
-        <v>1.58</v>
+        <v>-0.43</v>
+      </c>
+      <c r="I60" s="44" t="n">
+        <v>3.6</v>
       </c>
       <c r="J60" s="40" t="n">
-        <v>-0.15</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="61" customHeight="true" ht="21.75">
@@ -2666,27 +2666,27 @@
         </is>
       </c>
       <c r="D61" s="27" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>1.43</v>
+        <v>2.87</v>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="H61" s="41" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="I61" s="42" t="n">
-        <v>1.58</v>
+        <v>-0.43</v>
+      </c>
+      <c r="I61" s="45" t="n">
+        <v>3.6</v>
       </c>
       <c r="J61" s="42" t="n">
-        <v>-0.15</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="62" customHeight="true" ht="21.75">
@@ -2698,13 +2698,13 @@
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
       <c r="D62" s="14" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="E62" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="H62" s="37" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I62" s="38" t="n">
-        <v>0.79</v>
+        <v>0.43</v>
+      </c>
+      <c r="I62" s="18" t="n">
+        <v>1.0</v>
       </c>
       <c r="J62" s="38" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="63" customHeight="true" ht="21.75">
@@ -2734,13 +2734,13 @@
       </c>
       <c r="C63" s="20"/>
       <c r="D63" s="21" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="E63" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="H63" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I63" s="40" t="n">
-        <v>0.79</v>
+        <v>0.43</v>
+      </c>
+      <c r="I63" s="25" t="n">
+        <v>1.0</v>
       </c>
       <c r="J63" s="40" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="64" customHeight="true" ht="21.75">
@@ -2770,27 +2770,27 @@
         </is>
       </c>
       <c r="D64" s="32" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="E64" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F64" s="33" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="G64" s="34" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H64" s="48" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I64" s="47" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J64" s="47" t="n">
-        <v>0.51</v>
+      <c r="H64" s="46" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I64" s="36" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J64" s="48" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="65" customHeight="true" ht="21.75">
@@ -2802,24 +2802,24 @@
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
       <c r="D65" s="14" t="n">
-        <v>1.42</v>
+        <v>0.64</v>
       </c>
       <c r="E65" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H65" s="37" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I65" s="18" t="n">
-        <v>0.0</v>
+        <v>0.8</v>
+      </c>
+      <c r="I65" s="43" t="n">
+        <v>0.2</v>
       </c>
       <c r="J65" s="38" t="n">
         <v>0.9</v>
@@ -2838,24 +2838,24 @@
       </c>
       <c r="C66" s="20"/>
       <c r="D66" s="21" t="n">
-        <v>1.42</v>
+        <v>0.64</v>
       </c>
       <c r="E66" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G66" s="23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H66" s="39" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I66" s="25" t="n">
-        <v>0.0</v>
+        <v>0.8</v>
+      </c>
+      <c r="I66" s="44" t="n">
+        <v>0.2</v>
       </c>
       <c r="J66" s="40" t="n">
         <v>0.9</v>
@@ -2874,26 +2874,26 @@
         </is>
       </c>
       <c r="D67" s="27" t="n">
-        <v>1.42</v>
+        <v>0.64</v>
       </c>
       <c r="E67" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F67" s="28" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H67" s="49" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I67" s="31" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J67" s="44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I67" s="45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J67" s="45" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2917,10 +2917,10 @@
         <v>0.0</v>
       </c>
       <c r="I68" s="50" t="n">
-        <v>99.92</v>
+        <v>100.1</v>
       </c>
       <c r="J68" s="50" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>

--- a/weeks/undefined_20260929.xlsx
+++ b/weeks/undefined_20260929.xlsx
@@ -359,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
@@ -487,9 +487,6 @@
     <xf numFmtId="164" fontId="25" fillId="8" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="19" fillId="7" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
@@ -505,7 +502,7 @@
     <xf numFmtId="164" fontId="30" fillId="6" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="8" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="166" fontId="29" fillId="6" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="17" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
@@ -616,13 +613,13 @@
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="n">
-        <v>2.72</v>
+        <v>0.0</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>3.92</v>
+        <v>0.0</v>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
@@ -630,13 +627,13 @@
         </is>
       </c>
       <c r="H3" s="37" t="n">
-        <v>3.92</v>
+        <v>0.0</v>
       </c>
       <c r="I3" s="18" t="n">
         <v>0.0</v>
       </c>
       <c r="J3" s="38" t="n">
-        <v>3.92</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4" customHeight="true" ht="21.75">
@@ -652,13 +649,13 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="21" t="n">
-        <v>2.72</v>
+        <v>0.0</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>3.92</v>
+        <v>0.0</v>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
@@ -666,13 +663,13 @@
         </is>
       </c>
       <c r="H4" s="39" t="n">
-        <v>3.92</v>
+        <v>0.0</v>
       </c>
       <c r="I4" s="25" t="n">
         <v>0.0</v>
       </c>
       <c r="J4" s="40" t="n">
-        <v>3.92</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5" customHeight="true" ht="21.75">
@@ -688,27 +685,27 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>2.72</v>
+        <v>0.0</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>2.72</v>
+        <v>0.0</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>3.92</v>
+        <v>0.0</v>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="41" t="n">
-        <v>3.92</v>
+      <c r="H5" s="30" t="n">
+        <v>0.0</v>
       </c>
       <c r="I5" s="31" t="n">
         <v>0.0</v>
       </c>
-      <c r="J5" s="42" t="n">
-        <v>3.92</v>
+      <c r="J5" s="31" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" customHeight="true" ht="21.75">
@@ -746,27 +743,27 @@
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="14" t="n">
-        <v>23.48</v>
+        <v>35.94</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>20.05</v>
+        <v>32.64</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="H7" s="37" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="I7" s="43" t="n">
-        <v>19.2</v>
+        <v>4.04</v>
+      </c>
+      <c r="I7" s="38" t="n">
+        <v>30.21</v>
       </c>
       <c r="J7" s="38" t="n">
-        <v>0.85</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="21.75">
@@ -782,27 +779,27 @@
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="21" t="n">
-        <v>11.8</v>
+        <v>9.21</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>8.73</v>
+        <v>9.68</v>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H8" s="39" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I8" s="44" t="n">
-        <v>8.1</v>
+        <v>0.68</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>8.91</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="9" customHeight="true" ht="21.75">
@@ -818,27 +815,27 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>11.8</v>
+        <v>9.21</v>
       </c>
       <c r="E9" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>8.73</v>
+        <v>9.68</v>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H9" s="41" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I9" s="45" t="n">
-        <v>8.1</v>
+        <v>0.68</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>8.91</v>
       </c>
       <c r="J9" s="42" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="10" customHeight="true" ht="21.75">
@@ -854,27 +851,27 @@
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="21" t="n">
-        <v>8.69</v>
+        <v>7.57</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>8.45</v>
+        <v>8.25</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="H10" s="39" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I10" s="44" t="n">
-        <v>8.1</v>
+        <v>-0.35</v>
+      </c>
+      <c r="I10" s="43" t="n">
+        <v>9.1</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>0.35</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="11" customHeight="true" ht="21.75">
@@ -890,27 +887,27 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>8.69</v>
+        <v>7.57</v>
       </c>
       <c r="E11" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>8.45</v>
+        <v>8.25</v>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="H11" s="41" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I11" s="45" t="n">
-        <v>8.1</v>
+        <v>-0.35</v>
+      </c>
+      <c r="I11" s="44" t="n">
+        <v>9.1</v>
       </c>
       <c r="J11" s="42" t="n">
-        <v>0.35</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="12" customHeight="true" ht="21.75">
@@ -926,27 +923,27 @@
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" t="n">
-        <v>2.39</v>
+        <v>16.7</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>2.64</v>
+        <v>13.24</v>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H12" s="39" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="I12" s="25" t="n">
-        <v>3.0</v>
+        <v>3.44</v>
+      </c>
+      <c r="I12" s="40" t="n">
+        <v>11.88</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>-0.36</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="13" customHeight="true" ht="21.75">
@@ -962,27 +959,27 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>2.39</v>
+        <v>16.7</v>
       </c>
       <c r="E13" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F13" s="28" t="n">
-        <v>2.64</v>
+        <v>13.24</v>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H13" s="41" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="I13" s="31" t="n">
-        <v>3.0</v>
+        <v>3.44</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>11.88</v>
       </c>
       <c r="J13" s="42" t="n">
-        <v>-0.36</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="14" customHeight="true" ht="21.75">
@@ -998,27 +995,27 @@
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" t="n">
-        <v>0.6</v>
+        <v>2.46</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.23</v>
+        <v>1.47</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="H14" s="39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I14" s="25" t="n">
-        <v>0.0</v>
+        <v>0.27</v>
+      </c>
+      <c r="I14" s="40" t="n">
+        <v>0.32</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>0.23</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="15" customHeight="true" ht="21.75">
@@ -1034,27 +1031,27 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>0.6</v>
+        <v>2.46</v>
       </c>
       <c r="E15" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>0.23</v>
+        <v>1.47</v>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="H15" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I15" s="31" t="n">
-        <v>0.0</v>
+        <v>0.27</v>
+      </c>
+      <c r="I15" s="42" t="n">
+        <v>0.32</v>
       </c>
       <c r="J15" s="42" t="n">
-        <v>0.23</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="16" customHeight="true" ht="21.75">
@@ -1066,27 +1063,27 @@
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="14" t="n">
-        <v>8.33</v>
+        <v>5.91</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>6.47</v>
+        <v>8.2</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H16" s="37" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I16" s="43" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
+      </c>
+      <c r="I16" s="38" t="n">
+        <v>6.39</v>
       </c>
       <c r="J16" s="38" t="n">
-        <v>1.07</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="17" customHeight="true" ht="21.75">
@@ -1102,27 +1099,27 @@
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>2.14</v>
+        <v>2.83</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H17" s="39" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I17" s="44" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
+      </c>
+      <c r="I17" s="43" t="n">
+        <v>1.5</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>0.74</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="18" customHeight="true" ht="21.75">
@@ -1138,27 +1135,27 @@
         </is>
       </c>
       <c r="D18" s="32" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="H18" s="46" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I18" s="47" t="n">
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H18" s="45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I18" s="46" t="n">
         <v>1.2</v>
       </c>
-      <c r="J18" s="48" t="n">
-        <v>0.59</v>
+      <c r="J18" s="47" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="19" customHeight="true" ht="21.75">
@@ -1180,21 +1177,21 @@
         <v>0.0</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H19" s="41" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I19" s="45" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
+      </c>
+      <c r="I19" s="44" t="n">
+        <v>0.3</v>
       </c>
       <c r="J19" s="42" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="20" customHeight="true" ht="21.75">
@@ -1210,27 +1207,27 @@
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" t="n">
-        <v>4.88</v>
+        <v>3.55</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>3.24</v>
+        <v>4.33</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="H20" s="39" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I20" s="44" t="n">
-        <v>3.1</v>
+        <v>0.83</v>
+      </c>
+      <c r="I20" s="40" t="n">
+        <v>3.74</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>0.14</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="21" customHeight="true" ht="21.75">
@@ -1246,13 +1243,13 @@
         </is>
       </c>
       <c r="D21" s="27" t="n">
-        <v>4.36</v>
+        <v>2.9</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>2.34</v>
+        <v>3.43</v>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
@@ -1260,13 +1257,13 @@
         </is>
       </c>
       <c r="H21" s="41" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I21" s="45" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
+      </c>
+      <c r="I21" s="42" t="n">
+        <v>2.44</v>
       </c>
       <c r="J21" s="42" t="n">
-        <v>0.64</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="22" customHeight="true" ht="21.75">
@@ -1282,7 +1279,7 @@
         </is>
       </c>
       <c r="D22" s="32" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>0.0</v>
@@ -1292,17 +1289,17 @@
       </c>
       <c r="G22" s="34" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H22" s="35" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J22" s="47" t="n">
-        <v>-0.5</v>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H22" s="48" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I22" s="46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" s="46" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="23" customHeight="true" ht="21.75">
@@ -1318,27 +1315,27 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" t="n">
-        <v>1.3</v>
+        <v>0.69</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="H23" s="39" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="I23" s="44" t="n">
-        <v>0.9</v>
+        <v>-0.16</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>1.15</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>0.19</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="21.75">
@@ -1354,27 +1351,27 @@
         </is>
       </c>
       <c r="D24" s="32" t="n">
-        <v>1.3</v>
+        <v>0.69</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G24" s="34" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="H24" s="46" t="n">
-        <v>-0.21</v>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="H24" s="45" t="n">
+        <v>-0.16</v>
       </c>
       <c r="I24" s="47" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J24" s="48" t="n">
-        <v>0.19</v>
+        <v>1.15</v>
+      </c>
+      <c r="J24" s="47" t="n">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="25" customHeight="true" ht="21.75">
@@ -1386,27 +1383,27 @@
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="14" t="n">
-        <v>6.46</v>
+        <v>7.72</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>7.31</v>
+        <v>7.16</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="H25" s="37" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I25" s="43" t="n">
-        <v>7.7</v>
+        <v>-0.74</v>
+      </c>
+      <c r="I25" s="38" t="n">
+        <v>8.43</v>
       </c>
       <c r="J25" s="38" t="n">
-        <v>-0.39</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="21.75">
@@ -1422,27 +1419,27 @@
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" t="n">
-        <v>4.82</v>
+        <v>6.14</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>5.56</v>
+        <v>5.77</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="H26" s="39" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="I26" s="44" t="n">
-        <v>5.8</v>
+        <v>-0.33</v>
+      </c>
+      <c r="I26" s="40" t="n">
+        <v>6.71</v>
       </c>
       <c r="J26" s="40" t="n">
-        <v>-0.24</v>
+        <v>-0.94</v>
       </c>
     </row>
     <row r="27" customHeight="true" ht="21.75">
@@ -1458,27 +1455,27 @@
         </is>
       </c>
       <c r="D27" s="27" t="n">
-        <v>4.82</v>
+        <v>6.14</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>5.56</v>
+        <v>5.77</v>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="H27" s="41" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="I27" s="45" t="n">
-        <v>5.8</v>
+        <v>-0.33</v>
+      </c>
+      <c r="I27" s="42" t="n">
+        <v>6.71</v>
       </c>
       <c r="J27" s="42" t="n">
-        <v>-0.24</v>
+        <v>-0.94</v>
       </c>
     </row>
     <row r="28" customHeight="true" ht="21.75">
@@ -1494,27 +1491,27 @@
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H28" s="39" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I28" s="44" t="n">
-        <v>1.9</v>
+        <v>-0.41</v>
+      </c>
+      <c r="I28" s="40" t="n">
+        <v>1.72</v>
       </c>
       <c r="J28" s="40" t="n">
-        <v>-0.15</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="29" customHeight="true" ht="21.75">
@@ -1530,27 +1527,27 @@
         </is>
       </c>
       <c r="D29" s="27" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="E29" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F29" s="28" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H29" s="41" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I29" s="45" t="n">
-        <v>1.9</v>
+        <v>-0.41</v>
+      </c>
+      <c r="I29" s="42" t="n">
+        <v>1.72</v>
       </c>
       <c r="J29" s="42" t="n">
-        <v>-0.15</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="30" customHeight="true" ht="21.75">
@@ -1562,27 +1559,27 @@
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="14" t="n">
-        <v>11.41</v>
+        <v>13.54</v>
       </c>
       <c r="E30" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>13.06</v>
+        <v>13.75</v>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H30" s="37" t="n">
-        <v>-3.34</v>
-      </c>
-      <c r="I30" s="43" t="n">
-        <v>17.2</v>
+        <v>-2.25</v>
+      </c>
+      <c r="I30" s="38" t="n">
+        <v>15.82</v>
       </c>
       <c r="J30" s="38" t="n">
-        <v>-4.14</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="31" customHeight="true" ht="21.75">
@@ -1598,27 +1595,27 @@
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" t="n">
-        <v>0.95</v>
+        <v>3.42</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="H31" s="39" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I31" s="44" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
+      </c>
+      <c r="I31" s="40" t="n">
+        <v>2.97</v>
       </c>
       <c r="J31" s="40" t="n">
-        <v>-0.12</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="32" customHeight="true" ht="21.75">
@@ -1634,27 +1631,27 @@
         </is>
       </c>
       <c r="D32" s="32" t="n">
-        <v>0.95</v>
+        <v>3.42</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F32" s="33" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H32" s="46" t="n">
-        <v>0.18</v>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="H32" s="48" t="n">
+        <v>0.1</v>
       </c>
       <c r="I32" s="47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J32" s="48" t="n">
-        <v>-0.12</v>
+        <v>2.97</v>
+      </c>
+      <c r="J32" s="47" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="33" customHeight="true" ht="21.75">
@@ -1670,27 +1667,27 @@
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" t="n">
-        <v>4.57</v>
+        <v>0.0</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>5.89</v>
+        <v>2.5</v>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="H33" s="39" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="I33" s="44" t="n">
-        <v>8.1</v>
+        <v>-2.4</v>
+      </c>
+      <c r="I33" s="40" t="n">
+        <v>4.78</v>
       </c>
       <c r="J33" s="40" t="n">
-        <v>-2.21</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="34" customHeight="true" ht="21.75">
@@ -1706,27 +1703,27 @@
         </is>
       </c>
       <c r="D34" s="32" t="n">
-        <v>4.57</v>
+        <v>0.0</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F34" s="33" t="n">
-        <v>5.89</v>
+        <v>2.5</v>
       </c>
       <c r="G34" s="34" t="inlineStr">
         <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="H34" s="46" t="n">
-        <v>-1.91</v>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="H34" s="48" t="n">
+        <v>-2.4</v>
       </c>
       <c r="I34" s="47" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J34" s="48" t="n">
-        <v>-2.21</v>
+        <v>4.78</v>
+      </c>
+      <c r="J34" s="47" t="n">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="35" customHeight="true" ht="21.75">
@@ -1742,27 +1739,27 @@
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" t="n">
-        <v>5.89</v>
+        <v>10.12</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>3.99</v>
+        <v>8.05</v>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H35" s="39" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="I35" s="44" t="n">
-        <v>5.8</v>
+        <v>0.05</v>
+      </c>
+      <c r="I35" s="40" t="n">
+        <v>8.07</v>
       </c>
       <c r="J35" s="40" t="n">
-        <v>-1.81</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="36" customHeight="true" ht="21.75">
@@ -1778,27 +1775,27 @@
         </is>
       </c>
       <c r="D36" s="32" t="n">
-        <v>5.89</v>
+        <v>10.12</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F36" s="33" t="n">
-        <v>3.99</v>
+        <v>8.05</v>
       </c>
       <c r="G36" s="34" t="inlineStr">
         <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="H36" s="46" t="n">
-        <v>-1.61</v>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H36" s="45" t="n">
+        <v>0.05</v>
       </c>
       <c r="I36" s="47" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J36" s="48" t="n">
-        <v>-1.81</v>
+        <v>8.07</v>
+      </c>
+      <c r="J36" s="47" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="37" customHeight="true" ht="21.75">
@@ -1810,27 +1807,27 @@
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="14" t="n">
-        <v>15.86</v>
+        <v>12.29</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>14.06</v>
+        <v>13.7</v>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H37" s="37" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I37" s="43" t="n">
-        <v>14.2</v>
+        <v>-1.3</v>
+      </c>
+      <c r="I37" s="38" t="n">
+        <v>14.89</v>
       </c>
       <c r="J37" s="38" t="n">
-        <v>-0.14</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="38" customHeight="true" ht="21.75">
@@ -1846,27 +1843,27 @@
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" t="n">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>3.23</v>
+        <v>3.74</v>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="H38" s="39" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="I38" s="44" t="n">
-        <v>3.2</v>
+        <v>-0.56</v>
+      </c>
+      <c r="I38" s="40" t="n">
+        <v>3.66</v>
       </c>
       <c r="J38" s="40" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="39" customHeight="true" ht="21.75">
@@ -1882,27 +1879,27 @@
         </is>
       </c>
       <c r="D39" s="27" t="n">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>3.23</v>
+        <v>3.74</v>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="H39" s="41" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="I39" s="45" t="n">
-        <v>3.2</v>
+        <v>-0.56</v>
+      </c>
+      <c r="I39" s="42" t="n">
+        <v>3.66</v>
       </c>
       <c r="J39" s="42" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="40" customHeight="true" ht="21.75">
@@ -1918,27 +1915,27 @@
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" t="n">
-        <v>5.27</v>
+        <v>4.2</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>5.3</v>
+        <v>4.73</v>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="H40" s="39" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I40" s="44" t="n">
-        <v>5.3</v>
+        <v>-1.07</v>
+      </c>
+      <c r="I40" s="40" t="n">
+        <v>6.57</v>
       </c>
       <c r="J40" s="40" t="n">
-        <v>0.0</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="41" customHeight="true" ht="21.75">
@@ -1954,27 +1951,27 @@
         </is>
       </c>
       <c r="D41" s="27" t="n">
-        <v>5.27</v>
+        <v>4.2</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>5.3</v>
+        <v>4.73</v>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H41" s="49" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I41" s="45" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J41" s="31" t="n">
-        <v>0.0</v>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="H41" s="41" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="I41" s="42" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="J41" s="42" t="n">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="42" customHeight="true" ht="21.75">
@@ -1990,27 +1987,27 @@
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="21" t="n">
-        <v>7.27</v>
+        <v>3.89</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>5.53</v>
+        <v>5.23</v>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="H42" s="39" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="I42" s="44" t="n">
-        <v>5.7</v>
+        <v>0.33</v>
+      </c>
+      <c r="I42" s="40" t="n">
+        <v>4.66</v>
       </c>
       <c r="J42" s="40" t="n">
-        <v>-0.17</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="43" customHeight="true" ht="21.75">
@@ -2026,27 +2023,27 @@
         </is>
       </c>
       <c r="D43" s="27" t="n">
-        <v>7.27</v>
+        <v>3.89</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5.53</v>
+        <v>5.23</v>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="H43" s="41" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="I43" s="45" t="n">
-        <v>5.7</v>
+        <v>0.33</v>
+      </c>
+      <c r="I43" s="42" t="n">
+        <v>4.66</v>
       </c>
       <c r="J43" s="42" t="n">
-        <v>-0.17</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="44" customHeight="true" ht="21.75">
@@ -2058,27 +2055,27 @@
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="14" t="n">
-        <v>14.45</v>
+        <v>13.01</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>16.21</v>
+        <v>12.34</v>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="H44" s="37" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I44" s="43" t="n">
-        <v>14.9</v>
+        <v>0.54</v>
+      </c>
+      <c r="I44" s="38" t="n">
+        <v>10.81</v>
       </c>
       <c r="J44" s="38" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="45" customHeight="true" ht="21.75">
@@ -2094,27 +2091,27 @@
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="21" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="E45" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>6.32</v>
+        <v>6.47</v>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="H45" s="39" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I45" s="44" t="n">
-        <v>5.1</v>
+        <v>1.27</v>
+      </c>
+      <c r="I45" s="40" t="n">
+        <v>4.41</v>
       </c>
       <c r="J45" s="40" t="n">
-        <v>1.22</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="46" customHeight="true" ht="21.75">
@@ -2130,27 +2127,27 @@
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="E46" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F46" s="33" t="n">
-        <v>6.32</v>
+        <v>6.47</v>
       </c>
       <c r="G46" s="34" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="H46" s="46" t="n">
-        <v>0.82</v>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="H46" s="45" t="n">
+        <v>1.27</v>
       </c>
       <c r="I46" s="47" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J46" s="48" t="n">
-        <v>1.22</v>
+        <v>4.41</v>
+      </c>
+      <c r="J46" s="47" t="n">
+        <v>2.06</v>
       </c>
     </row>
     <row r="47" customHeight="true" ht="21.75">
@@ -2166,27 +2163,27 @@
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="21" t="n">
-        <v>4.98</v>
+        <v>4.72</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>6.31</v>
+        <v>4.61</v>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="H47" s="39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I47" s="44" t="n">
-        <v>4.9</v>
+        <v>-0.19</v>
+      </c>
+      <c r="I47" s="40" t="n">
+        <v>4.56</v>
       </c>
       <c r="J47" s="40" t="n">
-        <v>1.41</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="48" customHeight="true" ht="21.75">
@@ -2202,27 +2199,27 @@
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="E48" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F48" s="33" t="n">
-        <v>3.56</v>
+        <v>2.68</v>
       </c>
       <c r="G48" s="34" t="inlineStr">
         <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="H48" s="46" t="n">
-        <v>-1.14</v>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="H48" s="45" t="n">
+        <v>-2.12</v>
       </c>
       <c r="I48" s="47" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J48" s="48" t="n">
-        <v>-1.34</v>
+        <v>4.56</v>
+      </c>
+      <c r="J48" s="47" t="n">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="49" customHeight="true" ht="21.75">
@@ -2238,13 +2235,13 @@
         </is>
       </c>
       <c r="D49" s="27" t="n">
-        <v>1.18</v>
+        <v>2.27</v>
       </c>
       <c r="E49" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
@@ -2252,13 +2249,13 @@
         </is>
       </c>
       <c r="H49" s="41" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="I49" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J49" s="42" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="50" customHeight="true" ht="21.75">
@@ -2274,27 +2271,27 @@
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="21" t="n">
-        <v>3.49</v>
+        <v>2.28</v>
       </c>
       <c r="E50" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>3.58</v>
+        <v>1.26</v>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H50" s="39" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="I50" s="44" t="n">
-        <v>4.9</v>
+        <v>-0.54</v>
+      </c>
+      <c r="I50" s="40" t="n">
+        <v>1.84</v>
       </c>
       <c r="J50" s="40" t="n">
-        <v>-1.32</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="51" customHeight="true" ht="21.75">
@@ -2310,27 +2307,27 @@
         </is>
       </c>
       <c r="D51" s="27" t="n">
-        <v>3.49</v>
+        <v>2.28</v>
       </c>
       <c r="E51" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F51" s="28" t="n">
-        <v>3.58</v>
+        <v>1.26</v>
       </c>
       <c r="G51" s="29" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H51" s="41" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="I51" s="45" t="n">
-        <v>4.9</v>
+        <v>-0.54</v>
+      </c>
+      <c r="I51" s="42" t="n">
+        <v>1.84</v>
       </c>
       <c r="J51" s="42" t="n">
-        <v>-1.32</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="52" customHeight="true" ht="21.75">
@@ -2342,27 +2339,27 @@
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="14" t="n">
-        <v>15.02</v>
+        <v>10.49</v>
       </c>
       <c r="E52" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>16.19</v>
+        <v>10.71</v>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="H52" s="37" t="n">
-        <v>-2.91</v>
-      </c>
-      <c r="I52" s="43" t="n">
-        <v>20.3</v>
+        <v>-2.09</v>
+      </c>
+      <c r="I52" s="38" t="n">
+        <v>12.58</v>
       </c>
       <c r="J52" s="38" t="n">
-        <v>-4.11</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="53" customHeight="true" ht="21.75">
@@ -2378,27 +2375,27 @@
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="21" t="n">
-        <v>3.37</v>
+        <v>2.96</v>
       </c>
       <c r="E53" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="H53" s="39" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="I53" s="44" t="n">
-        <v>4.7</v>
+        <v>0.18</v>
+      </c>
+      <c r="I53" s="40" t="n">
+        <v>2.32</v>
       </c>
       <c r="J53" s="40" t="n">
-        <v>-1.52</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="21.75">
@@ -2414,27 +2411,27 @@
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>3.37</v>
+        <v>2.96</v>
       </c>
       <c r="E54" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F54" s="33" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="G54" s="34" t="inlineStr">
         <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="H54" s="46" t="n">
-        <v>-1.22</v>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="H54" s="45" t="n">
+        <v>0.18</v>
       </c>
       <c r="I54" s="47" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J54" s="48" t="n">
-        <v>-1.52</v>
+        <v>2.32</v>
+      </c>
+      <c r="J54" s="47" t="n">
+        <v>0.56</v>
       </c>
     </row>
     <row r="55" customHeight="true" ht="21.75">
@@ -2450,27 +2447,27 @@
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="21" t="n">
-        <v>5.93</v>
+        <v>4.51</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>6.95</v>
+        <v>4.89</v>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H55" s="39" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I55" s="44" t="n">
-        <v>7.7</v>
+        <v>-1.11</v>
+      </c>
+      <c r="I55" s="40" t="n">
+        <v>5.82</v>
       </c>
       <c r="J55" s="40" t="n">
-        <v>-0.75</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="56" customHeight="true" ht="21.75">
@@ -2486,27 +2483,27 @@
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>4.99</v>
+        <v>3.78</v>
       </c>
       <c r="E56" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F56" s="33" t="n">
-        <v>6.11</v>
+        <v>4.48</v>
       </c>
       <c r="G56" s="34" t="inlineStr">
         <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="H56" s="46" t="n">
-        <v>-1.29</v>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H56" s="45" t="n">
+        <v>-1.52</v>
       </c>
       <c r="I56" s="47" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J56" s="48" t="n">
-        <v>-1.59</v>
+        <v>5.82</v>
+      </c>
+      <c r="J56" s="47" t="n">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="57" customHeight="true" ht="21.75">
@@ -2522,13 +2519,13 @@
         </is>
       </c>
       <c r="D57" s="27" t="n">
-        <v>0.94</v>
+        <v>0.73</v>
       </c>
       <c r="E57" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F57" s="28" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
@@ -2536,13 +2533,13 @@
         </is>
       </c>
       <c r="H57" s="41" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="I57" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J57" s="42" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="58" customHeight="true" ht="21.75">
@@ -2558,27 +2555,27 @@
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="21" t="n">
-        <v>2.77</v>
+        <v>1.3</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F58" s="22" t="n">
-        <v>3.19</v>
+        <v>1.72</v>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="H58" s="39" t="n">
-        <v>-0.81</v>
-      </c>
-      <c r="I58" s="44" t="n">
-        <v>4.3</v>
+        <v>-0.78</v>
+      </c>
+      <c r="I58" s="40" t="n">
+        <v>2.86</v>
       </c>
       <c r="J58" s="40" t="n">
-        <v>-1.11</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="59" customHeight="true" ht="21.75">
@@ -2594,27 +2591,27 @@
         </is>
       </c>
       <c r="D59" s="27" t="n">
-        <v>2.77</v>
+        <v>1.3</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>3.19</v>
+        <v>1.72</v>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="H59" s="41" t="n">
-        <v>-0.81</v>
-      </c>
-      <c r="I59" s="45" t="n">
-        <v>4.3</v>
+        <v>-0.78</v>
+      </c>
+      <c r="I59" s="42" t="n">
+        <v>2.86</v>
       </c>
       <c r="J59" s="42" t="n">
-        <v>-1.11</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="21.75">
@@ -2630,27 +2627,27 @@
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="21" t="n">
-        <v>2.95</v>
+        <v>1.72</v>
       </c>
       <c r="E60" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>2.87</v>
+        <v>1.22</v>
       </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H60" s="39" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="I60" s="44" t="n">
-        <v>3.6</v>
+        <v>-0.38</v>
+      </c>
+      <c r="I60" s="40" t="n">
+        <v>1.58</v>
       </c>
       <c r="J60" s="40" t="n">
-        <v>-0.73</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="61" customHeight="true" ht="21.75">
@@ -2666,27 +2663,27 @@
         </is>
       </c>
       <c r="D61" s="27" t="n">
-        <v>2.95</v>
+        <v>1.72</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>2.87</v>
+        <v>1.22</v>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H61" s="41" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="I61" s="45" t="n">
-        <v>3.6</v>
+        <v>-0.38</v>
+      </c>
+      <c r="I61" s="42" t="n">
+        <v>1.58</v>
       </c>
       <c r="J61" s="42" t="n">
-        <v>-0.73</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="62" customHeight="true" ht="21.75">
@@ -2698,13 +2695,13 @@
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
       <c r="D62" s="14" t="n">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="E62" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>1.63</v>
+        <v>0.89</v>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
@@ -2712,13 +2709,13 @@
         </is>
       </c>
       <c r="H62" s="37" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I62" s="18" t="n">
-        <v>1.0</v>
+        <v>-0.31</v>
+      </c>
+      <c r="I62" s="38" t="n">
+        <v>0.79</v>
       </c>
       <c r="J62" s="38" t="n">
-        <v>0.63</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="63" customHeight="true" ht="21.75">
@@ -2734,13 +2731,13 @@
       </c>
       <c r="C63" s="20"/>
       <c r="D63" s="21" t="n">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="E63" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>1.63</v>
+        <v>0.89</v>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
@@ -2748,13 +2745,13 @@
         </is>
       </c>
       <c r="H63" s="39" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I63" s="25" t="n">
-        <v>1.0</v>
+        <v>-0.31</v>
+      </c>
+      <c r="I63" s="40" t="n">
+        <v>0.79</v>
       </c>
       <c r="J63" s="40" t="n">
-        <v>0.63</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="64" customHeight="true" ht="21.75">
@@ -2770,27 +2767,27 @@
         </is>
       </c>
       <c r="D64" s="32" t="n">
-        <v>1.63</v>
+        <v>1.1</v>
       </c>
       <c r="E64" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F64" s="33" t="n">
-        <v>1.63</v>
+        <v>0.89</v>
       </c>
       <c r="G64" s="34" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H64" s="46" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I64" s="36" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="J64" s="48" t="n">
-        <v>0.63</v>
+      <c r="H64" s="45" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="I64" s="47" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J64" s="46" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="65" customHeight="true" ht="21.75">
@@ -2802,27 +2799,27 @@
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
       <c r="D65" s="14" t="n">
-        <v>0.64</v>
+        <v>0.0</v>
       </c>
       <c r="E65" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>1.1</v>
+        <v>0.61</v>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H65" s="37" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I65" s="43" t="n">
-        <v>0.2</v>
+        <v>0.41</v>
+      </c>
+      <c r="I65" s="18" t="n">
+        <v>0.0</v>
       </c>
       <c r="J65" s="38" t="n">
-        <v>0.9</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="66" customHeight="true" ht="21.75">
@@ -2838,27 +2835,27 @@
       </c>
       <c r="C66" s="20"/>
       <c r="D66" s="21" t="n">
-        <v>0.64</v>
+        <v>0.0</v>
       </c>
       <c r="E66" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>1.1</v>
+        <v>0.61</v>
       </c>
       <c r="G66" s="23" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H66" s="39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I66" s="44" t="n">
-        <v>0.2</v>
+        <v>0.41</v>
+      </c>
+      <c r="I66" s="25" t="n">
+        <v>0.0</v>
       </c>
       <c r="J66" s="40" t="n">
-        <v>0.9</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="67" customHeight="true" ht="21.75">
@@ -2874,38 +2871,38 @@
         </is>
       </c>
       <c r="D67" s="27" t="n">
-        <v>0.64</v>
+        <v>0.0</v>
       </c>
       <c r="E67" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F67" s="28" t="n">
-        <v>1.1</v>
+        <v>0.61</v>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H67" s="49" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I67" s="45" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J67" s="45" t="n">
-        <v>0.9</v>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="H67" s="41" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I67" s="31" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J67" s="42" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
-      <c r="D68" s="50" t="n">
+      <c r="D68" s="49" t="n">
         <v>100.0</v>
       </c>
       <c r="E68" s="10"/>
-      <c r="F68" s="50" t="n">
+      <c r="F68" s="49" t="n">
         <v>100.0</v>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -2913,14 +2910,14 @@
           <t>100.00</t>
         </is>
       </c>
-      <c r="H68" s="51" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I68" s="50" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="J68" s="50" t="n">
-        <v>-0.1</v>
+      <c r="H68" s="50" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I68" s="49" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="J68" s="49" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/weeks/undefined_20260929.xlsx
+++ b/weeks/undefined_20260929.xlsx
@@ -359,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
@@ -487,6 +487,9 @@
     <xf numFmtId="164" fontId="25" fillId="8" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="7" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
@@ -500,6 +503,9 @@
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="30" fillId="6" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="8" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="29" fillId="6" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
@@ -613,13 +619,13 @@
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="n">
-        <v>0.0</v>
+        <v>2.96</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>0.0</v>
+        <v>2.67</v>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
@@ -627,13 +633,13 @@
         </is>
       </c>
       <c r="H3" s="37" t="n">
-        <v>0.0</v>
+        <v>2.67</v>
       </c>
       <c r="I3" s="18" t="n">
         <v>0.0</v>
       </c>
       <c r="J3" s="38" t="n">
-        <v>0.0</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="4" customHeight="true" ht="21.75">
@@ -649,13 +655,13 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="21" t="n">
-        <v>0.0</v>
+        <v>2.96</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>0.0</v>
+        <v>2.67</v>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
@@ -663,13 +669,13 @@
         </is>
       </c>
       <c r="H4" s="39" t="n">
-        <v>0.0</v>
+        <v>2.67</v>
       </c>
       <c r="I4" s="25" t="n">
         <v>0.0</v>
       </c>
       <c r="J4" s="40" t="n">
-        <v>0.0</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="5" customHeight="true" ht="21.75">
@@ -685,27 +691,27 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>0.0</v>
+        <v>2.96</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>0.0</v>
+        <v>2.96</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>0.0</v>
+        <v>2.67</v>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="30" t="n">
-        <v>0.0</v>
+      <c r="H5" s="41" t="n">
+        <v>2.67</v>
       </c>
       <c r="I5" s="31" t="n">
         <v>0.0</v>
       </c>
-      <c r="J5" s="31" t="n">
-        <v>0.0</v>
+      <c r="J5" s="42" t="n">
+        <v>2.67</v>
       </c>
     </row>
     <row r="6" customHeight="true" ht="21.75">
@@ -743,27 +749,27 @@
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="14" t="n">
-        <v>35.94</v>
+        <v>23.58</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>32.64</v>
+        <v>20.09</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="H7" s="37" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="I7" s="38" t="n">
-        <v>30.21</v>
+        <v>-0.71</v>
+      </c>
+      <c r="I7" s="43" t="n">
+        <v>19.2</v>
       </c>
       <c r="J7" s="38" t="n">
-        <v>2.43</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="21.75">
@@ -779,27 +785,27 @@
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="21" t="n">
-        <v>9.21</v>
+        <v>11.9</v>
       </c>
       <c r="E8" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>9.68</v>
+        <v>8.76</v>
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="H8" s="39" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I8" s="40" t="n">
-        <v>8.91</v>
+        <v>0.16</v>
+      </c>
+      <c r="I8" s="44" t="n">
+        <v>8.1</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="9" customHeight="true" ht="21.75">
@@ -815,27 +821,27 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>9.21</v>
+        <v>11.9</v>
       </c>
       <c r="E9" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>9.68</v>
+        <v>8.76</v>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="H9" s="41" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>8.91</v>
+        <v>0.16</v>
+      </c>
+      <c r="I9" s="45" t="n">
+        <v>8.1</v>
       </c>
       <c r="J9" s="42" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="10" customHeight="true" ht="21.75">
@@ -851,27 +857,27 @@
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="21" t="n">
-        <v>7.57</v>
+        <v>8.69</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>8.25</v>
+        <v>8.45</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="H10" s="39" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I10" s="43" t="n">
-        <v>9.1</v>
+        <v>0.35</v>
+      </c>
+      <c r="I10" s="44" t="n">
+        <v>8.1</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>-0.85</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="11" customHeight="true" ht="21.75">
@@ -887,27 +893,27 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>7.57</v>
+        <v>8.69</v>
       </c>
       <c r="E11" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>8.25</v>
+        <v>8.45</v>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="H11" s="41" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="I11" s="44" t="n">
-        <v>9.1</v>
+        <v>0.35</v>
+      </c>
+      <c r="I11" s="45" t="n">
+        <v>8.1</v>
       </c>
       <c r="J11" s="42" t="n">
-        <v>-0.85</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="12" customHeight="true" ht="21.75">
@@ -923,27 +929,27 @@
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="21" t="n">
-        <v>16.7</v>
+        <v>2.39</v>
       </c>
       <c r="E12" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>13.24</v>
+        <v>2.65</v>
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="H12" s="39" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="I12" s="40" t="n">
-        <v>11.88</v>
+        <v>-1.25</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>3.0</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>1.36</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="13" customHeight="true" ht="21.75">
@@ -959,27 +965,27 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>16.7</v>
+        <v>2.39</v>
       </c>
       <c r="E13" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F13" s="28" t="n">
-        <v>13.24</v>
+        <v>2.65</v>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="H13" s="41" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>11.88</v>
+        <v>-1.25</v>
+      </c>
+      <c r="I13" s="31" t="n">
+        <v>3.0</v>
       </c>
       <c r="J13" s="42" t="n">
-        <v>1.36</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="14" customHeight="true" ht="21.75">
@@ -995,27 +1001,27 @@
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" t="n">
-        <v>2.46</v>
+        <v>0.6</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>1.47</v>
+        <v>0.23</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H14" s="39" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I14" s="40" t="n">
-        <v>0.32</v>
+        <v>0.03</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>0.0</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>1.15</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="15" customHeight="true" ht="21.75">
@@ -1031,27 +1037,27 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>2.46</v>
+        <v>0.6</v>
       </c>
       <c r="E15" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>1.47</v>
+        <v>0.23</v>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H15" s="41" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>0.32</v>
+        <v>0.03</v>
+      </c>
+      <c r="I15" s="31" t="n">
+        <v>0.0</v>
       </c>
       <c r="J15" s="42" t="n">
-        <v>1.15</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="16" customHeight="true" ht="21.75">
@@ -1063,27 +1069,27 @@
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="14" t="n">
-        <v>5.91</v>
+        <v>7.81</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>8.2</v>
+        <v>6.54</v>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="H16" s="37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I16" s="38" t="n">
-        <v>6.39</v>
+        <v>0.94</v>
+      </c>
+      <c r="I16" s="43" t="n">
+        <v>5.4</v>
       </c>
       <c r="J16" s="38" t="n">
-        <v>1.81</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="17" customHeight="true" ht="21.75">
@@ -1099,27 +1105,27 @@
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="E17" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>2.83</v>
+        <v>2.13</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="H17" s="39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I17" s="43" t="n">
-        <v>1.5</v>
+        <v>0.73</v>
+      </c>
+      <c r="I17" s="44" t="n">
+        <v>1.4</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>1.33</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="18" customHeight="true" ht="21.75">
@@ -1135,27 +1141,27 @@
         </is>
       </c>
       <c r="D18" s="32" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="H18" s="45" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I18" s="46" t="n">
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="H18" s="46" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I18" s="47" t="n">
         <v>1.2</v>
       </c>
-      <c r="J18" s="47" t="n">
-        <v>1.15</v>
+      <c r="J18" s="48" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="19" customHeight="true" ht="21.75">
@@ -1177,21 +1183,21 @@
         <v>0.0</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="41" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I19" s="44" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
+      </c>
+      <c r="I19" s="45" t="n">
+        <v>0.2</v>
       </c>
       <c r="J19" s="42" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="20" customHeight="true" ht="21.75">
@@ -1207,27 +1213,27 @@
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" t="n">
-        <v>3.55</v>
+        <v>4.36</v>
       </c>
       <c r="E20" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>4.33</v>
+        <v>3.32</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="H20" s="39" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I20" s="40" t="n">
-        <v>3.74</v>
+        <v>0.42</v>
+      </c>
+      <c r="I20" s="44" t="n">
+        <v>3.1</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>0.59</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21" customHeight="true" ht="21.75">
@@ -1243,13 +1249,13 @@
         </is>
       </c>
       <c r="D21" s="27" t="n">
-        <v>2.9</v>
+        <v>4.36</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>3.43</v>
+        <v>2.35</v>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
@@ -1257,13 +1263,13 @@
         </is>
       </c>
       <c r="H21" s="41" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I21" s="42" t="n">
-        <v>2.44</v>
+        <v>0.35</v>
+      </c>
+      <c r="I21" s="45" t="n">
+        <v>1.7</v>
       </c>
       <c r="J21" s="42" t="n">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="22" customHeight="true" ht="21.75">
@@ -1279,27 +1285,27 @@
         </is>
       </c>
       <c r="D22" s="32" t="n">
-        <v>0.65</v>
+        <v>0.0</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F22" s="33" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="G22" s="34" t="inlineStr">
         <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="H22" s="48" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="I22" s="46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J22" s="46" t="n">
-        <v>-0.4</v>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="H22" s="46" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I22" s="47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J22" s="48" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="23" customHeight="true" ht="21.75">
@@ -1315,27 +1321,27 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" t="n">
-        <v>0.69</v>
+        <v>1.3</v>
       </c>
       <c r="E23" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="H23" s="39" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="I23" s="40" t="n">
-        <v>1.15</v>
+        <v>-0.21</v>
+      </c>
+      <c r="I23" s="44" t="n">
+        <v>0.9</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>-0.11</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="21.75">
@@ -1351,27 +1357,27 @@
         </is>
       </c>
       <c r="D24" s="32" t="n">
-        <v>0.69</v>
+        <v>1.3</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G24" s="34" t="inlineStr">
         <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="H24" s="45" t="n">
-        <v>-0.16</v>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="H24" s="46" t="n">
+        <v>-0.21</v>
       </c>
       <c r="I24" s="47" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J24" s="47" t="n">
-        <v>-0.11</v>
+        <v>0.9</v>
+      </c>
+      <c r="J24" s="48" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="25" customHeight="true" ht="21.75">
@@ -1383,27 +1389,27 @@
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="14" t="n">
-        <v>7.72</v>
+        <v>7.18</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>7.16</v>
+        <v>7.78</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="H25" s="37" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="I25" s="38" t="n">
-        <v>8.43</v>
+        <v>0.38</v>
+      </c>
+      <c r="I25" s="43" t="n">
+        <v>7.7</v>
       </c>
       <c r="J25" s="38" t="n">
-        <v>-1.27</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="21.75">
@@ -1419,27 +1425,27 @@
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" t="n">
-        <v>6.14</v>
+        <v>5.54</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>5.77</v>
+        <v>5.83</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="H26" s="39" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="I26" s="40" t="n">
-        <v>6.71</v>
+        <v>0.13</v>
+      </c>
+      <c r="I26" s="44" t="n">
+        <v>5.8</v>
       </c>
       <c r="J26" s="40" t="n">
-        <v>-0.94</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="27" customHeight="true" ht="21.75">
@@ -1455,27 +1461,27 @@
         </is>
       </c>
       <c r="D27" s="27" t="n">
-        <v>6.14</v>
+        <v>5.54</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>5.77</v>
+        <v>5.83</v>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="H27" s="41" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="I27" s="42" t="n">
-        <v>6.71</v>
+        <v>0.13</v>
+      </c>
+      <c r="I27" s="45" t="n">
+        <v>5.8</v>
       </c>
       <c r="J27" s="42" t="n">
-        <v>-0.94</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="28" customHeight="true" ht="21.75">
@@ -1491,27 +1497,27 @@
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>1.39</v>
+        <v>1.95</v>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="H28" s="39" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="I28" s="40" t="n">
-        <v>1.72</v>
+        <v>0.25</v>
+      </c>
+      <c r="I28" s="44" t="n">
+        <v>1.9</v>
       </c>
       <c r="J28" s="40" t="n">
-        <v>-0.33</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="29" customHeight="true" ht="21.75">
@@ -1527,27 +1533,27 @@
         </is>
       </c>
       <c r="D29" s="27" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="E29" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F29" s="28" t="n">
-        <v>1.39</v>
+        <v>1.95</v>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="H29" s="41" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="I29" s="42" t="n">
-        <v>1.72</v>
+        <v>0.25</v>
+      </c>
+      <c r="I29" s="45" t="n">
+        <v>1.9</v>
       </c>
       <c r="J29" s="42" t="n">
-        <v>-0.33</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="30" customHeight="true" ht="21.75">
@@ -1559,27 +1565,27 @@
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="14" t="n">
-        <v>13.54</v>
+        <v>10.73</v>
       </c>
       <c r="E30" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>13.75</v>
+        <v>12.54</v>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="H30" s="37" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="I30" s="38" t="n">
-        <v>15.82</v>
+        <v>-3.86</v>
+      </c>
+      <c r="I30" s="43" t="n">
+        <v>17.2</v>
       </c>
       <c r="J30" s="38" t="n">
-        <v>-2.07</v>
+        <v>-4.66</v>
       </c>
     </row>
     <row r="31" customHeight="true" ht="21.75">
@@ -1595,27 +1601,27 @@
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" t="n">
-        <v>3.42</v>
+        <v>0.95</v>
       </c>
       <c r="E31" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I31" s="40" t="n">
-        <v>2.97</v>
+        <v>0.17</v>
+      </c>
+      <c r="I31" s="44" t="n">
+        <v>3.3</v>
       </c>
       <c r="J31" s="40" t="n">
-        <v>0.23</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="32" customHeight="true" ht="21.75">
@@ -1631,27 +1637,27 @@
         </is>
       </c>
       <c r="D32" s="32" t="n">
-        <v>3.42</v>
+        <v>0.95</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F32" s="33" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="H32" s="48" t="n">
-        <v>0.1</v>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H32" s="46" t="n">
+        <v>0.17</v>
       </c>
       <c r="I32" s="47" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="J32" s="47" t="n">
-        <v>0.23</v>
+        <v>3.3</v>
+      </c>
+      <c r="J32" s="48" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="33" customHeight="true" ht="21.75">
@@ -1667,27 +1673,27 @@
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" t="n">
-        <v>0.0</v>
+        <v>4.24</v>
       </c>
       <c r="E33" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>2.5</v>
+        <v>5.51</v>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="H33" s="39" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="I33" s="40" t="n">
-        <v>4.78</v>
+        <v>-2.29</v>
+      </c>
+      <c r="I33" s="44" t="n">
+        <v>8.1</v>
       </c>
       <c r="J33" s="40" t="n">
-        <v>-2.28</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="34" customHeight="true" ht="21.75">
@@ -1703,27 +1709,27 @@
         </is>
       </c>
       <c r="D34" s="32" t="n">
-        <v>0.0</v>
+        <v>4.24</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F34" s="33" t="n">
-        <v>2.5</v>
+        <v>5.51</v>
       </c>
       <c r="G34" s="34" t="inlineStr">
         <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="H34" s="48" t="n">
-        <v>-2.4</v>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="H34" s="46" t="n">
+        <v>-2.29</v>
       </c>
       <c r="I34" s="47" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="J34" s="47" t="n">
-        <v>-2.28</v>
+        <v>8.1</v>
+      </c>
+      <c r="J34" s="48" t="n">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="35" customHeight="true" ht="21.75">
@@ -1739,27 +1745,27 @@
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" t="n">
-        <v>10.12</v>
+        <v>5.54</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>8.05</v>
+        <v>3.86</v>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="H35" s="39" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I35" s="40" t="n">
-        <v>8.07</v>
+        <v>-1.74</v>
+      </c>
+      <c r="I35" s="44" t="n">
+        <v>5.8</v>
       </c>
       <c r="J35" s="40" t="n">
-        <v>-0.02</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="36" customHeight="true" ht="21.75">
@@ -1775,27 +1781,27 @@
         </is>
       </c>
       <c r="D36" s="32" t="n">
-        <v>10.12</v>
+        <v>5.54</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F36" s="33" t="n">
-        <v>8.05</v>
+        <v>3.86</v>
       </c>
       <c r="G36" s="34" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H36" s="45" t="n">
-        <v>0.05</v>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="H36" s="46" t="n">
+        <v>-1.74</v>
       </c>
       <c r="I36" s="47" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="J36" s="47" t="n">
-        <v>-0.02</v>
+        <v>5.8</v>
+      </c>
+      <c r="J36" s="48" t="n">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="37" customHeight="true" ht="21.75">
@@ -1807,27 +1813,27 @@
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="14" t="n">
-        <v>12.29</v>
+        <v>16.42</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>13.7</v>
+        <v>14.7</v>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="H37" s="37" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="I37" s="38" t="n">
-        <v>14.89</v>
+        <v>0.2</v>
+      </c>
+      <c r="I37" s="43" t="n">
+        <v>14.2</v>
       </c>
       <c r="J37" s="38" t="n">
-        <v>-1.19</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" customHeight="true" ht="21.75">
@@ -1843,27 +1849,27 @@
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="E38" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>3.74</v>
+        <v>3.87</v>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="H38" s="39" t="n">
-        <v>-0.56</v>
-      </c>
-      <c r="I38" s="40" t="n">
-        <v>3.66</v>
+        <v>0.17</v>
+      </c>
+      <c r="I38" s="44" t="n">
+        <v>3.2</v>
       </c>
       <c r="J38" s="40" t="n">
-        <v>0.08</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="39" customHeight="true" ht="21.75">
@@ -1879,27 +1885,27 @@
         </is>
       </c>
       <c r="D39" s="27" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="E39" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F39" s="28" t="n">
-        <v>3.74</v>
+        <v>3.87</v>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="H39" s="41" t="n">
-        <v>-0.56</v>
-      </c>
-      <c r="I39" s="42" t="n">
-        <v>3.66</v>
+        <v>0.17</v>
+      </c>
+      <c r="I39" s="45" t="n">
+        <v>3.2</v>
       </c>
       <c r="J39" s="42" t="n">
-        <v>0.08</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="40" customHeight="true" ht="21.75">
@@ -1915,27 +1921,27 @@
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" t="n">
-        <v>4.2</v>
+        <v>5.27</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>4.73</v>
+        <v>5.3</v>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H40" s="39" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="I40" s="40" t="n">
-        <v>6.57</v>
+        <v>0.3</v>
+      </c>
+      <c r="I40" s="44" t="n">
+        <v>5.3</v>
       </c>
       <c r="J40" s="40" t="n">
-        <v>-1.84</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41" customHeight="true" ht="21.75">
@@ -1951,27 +1957,27 @@
         </is>
       </c>
       <c r="D41" s="27" t="n">
-        <v>4.2</v>
+        <v>5.27</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>4.73</v>
+        <v>5.3</v>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="H41" s="41" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="I41" s="42" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="J41" s="42" t="n">
-        <v>-1.84</v>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H41" s="49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I41" s="45" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J41" s="31" t="n">
+        <v>0.0</v>
       </c>
     </row>
     <row r="42" customHeight="true" ht="21.75">
@@ -1987,27 +1993,27 @@
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="21" t="n">
-        <v>3.89</v>
+        <v>7.27</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>5.23</v>
+        <v>5.53</v>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="H42" s="39" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I42" s="40" t="n">
-        <v>4.66</v>
+        <v>-0.27</v>
+      </c>
+      <c r="I42" s="44" t="n">
+        <v>5.7</v>
       </c>
       <c r="J42" s="40" t="n">
-        <v>0.57</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="43" customHeight="true" ht="21.75">
@@ -2023,27 +2029,27 @@
         </is>
       </c>
       <c r="D43" s="27" t="n">
-        <v>3.89</v>
+        <v>7.27</v>
       </c>
       <c r="E43" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F43" s="28" t="n">
-        <v>5.23</v>
+        <v>5.53</v>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="H43" s="41" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I43" s="42" t="n">
-        <v>4.66</v>
+        <v>-0.27</v>
+      </c>
+      <c r="I43" s="45" t="n">
+        <v>5.7</v>
       </c>
       <c r="J43" s="42" t="n">
-        <v>0.57</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="44" customHeight="true" ht="21.75">
@@ -2055,27 +2061,27 @@
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="14" t="n">
-        <v>13.01</v>
+        <v>14.0</v>
       </c>
       <c r="E44" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>12.34</v>
+        <v>16.14</v>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="H44" s="37" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I44" s="38" t="n">
-        <v>10.81</v>
+        <v>1.44</v>
+      </c>
+      <c r="I44" s="43" t="n">
+        <v>14.9</v>
       </c>
       <c r="J44" s="38" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="45" customHeight="true" ht="21.75">
@@ -2091,27 +2097,27 @@
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="21" t="n">
-        <v>6.01</v>
+        <v>5.98</v>
       </c>
       <c r="E45" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>6.47</v>
+        <v>6.32</v>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H45" s="39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="I45" s="40" t="n">
-        <v>4.41</v>
+        <v>0.82</v>
+      </c>
+      <c r="I45" s="44" t="n">
+        <v>5.1</v>
       </c>
       <c r="J45" s="40" t="n">
-        <v>2.06</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="46" customHeight="true" ht="21.75">
@@ -2127,27 +2133,27 @@
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>6.01</v>
+        <v>5.98</v>
       </c>
       <c r="E46" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F46" s="33" t="n">
-        <v>6.47</v>
+        <v>6.32</v>
       </c>
       <c r="G46" s="34" t="inlineStr">
         <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="H46" s="45" t="n">
-        <v>1.27</v>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H46" s="46" t="n">
+        <v>0.82</v>
       </c>
       <c r="I46" s="47" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="J46" s="47" t="n">
-        <v>2.06</v>
+        <v>5.1</v>
+      </c>
+      <c r="J46" s="48" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="47" customHeight="true" ht="21.75">
@@ -2163,27 +2169,27 @@
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="21" t="n">
-        <v>4.72</v>
+        <v>4.46</v>
       </c>
       <c r="E47" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>4.61</v>
+        <v>6.21</v>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="H47" s="39" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I47" s="40" t="n">
-        <v>4.56</v>
+        <v>1.51</v>
+      </c>
+      <c r="I47" s="44" t="n">
+        <v>4.9</v>
       </c>
       <c r="J47" s="40" t="n">
-        <v>0.05</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="48" customHeight="true" ht="21.75">
@@ -2199,27 +2205,27 @@
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="E48" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F48" s="33" t="n">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="G48" s="34" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="H48" s="45" t="n">
-        <v>-2.12</v>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="H48" s="50" t="n">
+        <v>-1.4</v>
       </c>
       <c r="I48" s="47" t="n">
-        <v>4.56</v>
+        <v>4.9</v>
       </c>
       <c r="J48" s="47" t="n">
-        <v>-1.88</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="49" customHeight="true" ht="21.75">
@@ -2235,13 +2241,13 @@
         </is>
       </c>
       <c r="D49" s="27" t="n">
-        <v>2.27</v>
+        <v>1.61</v>
       </c>
       <c r="E49" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F49" s="28" t="n">
-        <v>1.93</v>
+        <v>2.91</v>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
@@ -2249,13 +2255,13 @@
         </is>
       </c>
       <c r="H49" s="41" t="n">
-        <v>1.93</v>
+        <v>2.91</v>
       </c>
       <c r="I49" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J49" s="42" t="n">
-        <v>1.93</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="50" customHeight="true" ht="21.75">
@@ -2271,27 +2277,27 @@
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="21" t="n">
-        <v>2.28</v>
+        <v>3.56</v>
       </c>
       <c r="E50" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>1.26</v>
+        <v>3.61</v>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H50" s="39" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="I50" s="40" t="n">
-        <v>1.84</v>
+        <v>-0.89</v>
+      </c>
+      <c r="I50" s="44" t="n">
+        <v>4.9</v>
       </c>
       <c r="J50" s="40" t="n">
-        <v>-0.58</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="51" customHeight="true" ht="21.75">
@@ -2307,27 +2313,27 @@
         </is>
       </c>
       <c r="D51" s="27" t="n">
-        <v>2.28</v>
+        <v>3.56</v>
       </c>
       <c r="E51" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F51" s="28" t="n">
-        <v>1.26</v>
+        <v>3.61</v>
       </c>
       <c r="G51" s="29" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H51" s="41" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="I51" s="42" t="n">
-        <v>1.84</v>
+        <v>-0.89</v>
+      </c>
+      <c r="I51" s="45" t="n">
+        <v>4.9</v>
       </c>
       <c r="J51" s="42" t="n">
-        <v>-0.58</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="52" customHeight="true" ht="21.75">
@@ -2339,27 +2345,27 @@
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="14" t="n">
-        <v>10.49</v>
+        <v>15.05</v>
       </c>
       <c r="E52" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>10.71</v>
+        <v>16.6</v>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="H52" s="37" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I52" s="38" t="n">
-        <v>12.58</v>
+        <v>-2.5</v>
+      </c>
+      <c r="I52" s="43" t="n">
+        <v>20.3</v>
       </c>
       <c r="J52" s="38" t="n">
-        <v>-1.87</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="53" customHeight="true" ht="21.75">
@@ -2375,27 +2381,27 @@
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="21" t="n">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="E53" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="H53" s="39" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I53" s="40" t="n">
-        <v>2.32</v>
+        <v>-1.12</v>
+      </c>
+      <c r="I53" s="44" t="n">
+        <v>4.7</v>
       </c>
       <c r="J53" s="40" t="n">
-        <v>0.56</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="54" customHeight="true" ht="21.75">
@@ -2411,27 +2417,27 @@
         </is>
       </c>
       <c r="D54" s="32" t="n">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="E54" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F54" s="33" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="G54" s="34" t="inlineStr">
         <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="H54" s="45" t="n">
-        <v>0.18</v>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="H54" s="46" t="n">
+        <v>-1.12</v>
       </c>
       <c r="I54" s="47" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J54" s="47" t="n">
-        <v>0.56</v>
+        <v>4.7</v>
+      </c>
+      <c r="J54" s="48" t="n">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="55" customHeight="true" ht="21.75">
@@ -2447,27 +2453,27 @@
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="21" t="n">
-        <v>4.51</v>
+        <v>6.38</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>4.89</v>
+        <v>7.13</v>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="H55" s="39" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="I55" s="40" t="n">
-        <v>5.82</v>
+        <v>-0.27</v>
+      </c>
+      <c r="I55" s="44" t="n">
+        <v>7.7</v>
       </c>
       <c r="J55" s="40" t="n">
-        <v>-0.93</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="56" customHeight="true" ht="21.75">
@@ -2483,27 +2489,27 @@
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>3.78</v>
+        <v>5.44</v>
       </c>
       <c r="E56" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F56" s="33" t="n">
-        <v>4.48</v>
+        <v>6.29</v>
       </c>
       <c r="G56" s="34" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H56" s="45" t="n">
-        <v>-1.52</v>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="H56" s="46" t="n">
+        <v>-1.11</v>
       </c>
       <c r="I56" s="47" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="J56" s="47" t="n">
-        <v>-1.34</v>
+        <v>7.7</v>
+      </c>
+      <c r="J56" s="48" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="57" customHeight="true" ht="21.75">
@@ -2519,13 +2525,13 @@
         </is>
       </c>
       <c r="D57" s="27" t="n">
-        <v>0.73</v>
+        <v>0.94</v>
       </c>
       <c r="E57" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F57" s="28" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
@@ -2533,13 +2539,13 @@
         </is>
       </c>
       <c r="H57" s="41" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="I57" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J57" s="42" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="58" customHeight="true" ht="21.75">
@@ -2555,27 +2561,27 @@
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="21" t="n">
-        <v>1.3</v>
+        <v>2.77</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F58" s="22" t="n">
-        <v>1.72</v>
+        <v>3.44</v>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H58" s="39" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I58" s="40" t="n">
-        <v>2.86</v>
+        <v>-0.56</v>
+      </c>
+      <c r="I58" s="44" t="n">
+        <v>4.3</v>
       </c>
       <c r="J58" s="40" t="n">
-        <v>-1.14</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="59" customHeight="true" ht="21.75">
@@ -2591,27 +2597,27 @@
         </is>
       </c>
       <c r="D59" s="27" t="n">
-        <v>1.3</v>
+        <v>2.77</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>1.72</v>
+        <v>3.44</v>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H59" s="41" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I59" s="42" t="n">
-        <v>2.86</v>
+        <v>-0.56</v>
+      </c>
+      <c r="I59" s="45" t="n">
+        <v>4.3</v>
       </c>
       <c r="J59" s="42" t="n">
-        <v>-1.14</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="21.75">
@@ -2627,27 +2633,27 @@
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="21" t="n">
-        <v>1.72</v>
+        <v>2.66</v>
       </c>
       <c r="E60" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="H60" s="39" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="I60" s="40" t="n">
-        <v>1.58</v>
+        <v>-0.55</v>
+      </c>
+      <c r="I60" s="44" t="n">
+        <v>3.6</v>
       </c>
       <c r="J60" s="40" t="n">
-        <v>-0.36</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="61" customHeight="true" ht="21.75">
@@ -2663,27 +2669,27 @@
         </is>
       </c>
       <c r="D61" s="27" t="n">
-        <v>1.72</v>
+        <v>2.66</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="H61" s="41" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="I61" s="42" t="n">
-        <v>1.58</v>
+        <v>-0.55</v>
+      </c>
+      <c r="I61" s="45" t="n">
+        <v>3.6</v>
       </c>
       <c r="J61" s="42" t="n">
-        <v>-0.36</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="62" customHeight="true" ht="21.75">
@@ -2695,13 +2701,13 @@
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
       <c r="D62" s="14" t="n">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="E62" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>0.89</v>
+        <v>1.84</v>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
@@ -2709,13 +2715,13 @@
         </is>
       </c>
       <c r="H62" s="37" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="I62" s="38" t="n">
-        <v>0.79</v>
+        <v>0.64</v>
+      </c>
+      <c r="I62" s="18" t="n">
+        <v>1.0</v>
       </c>
       <c r="J62" s="38" t="n">
-        <v>0.1</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="63" customHeight="true" ht="21.75">
@@ -2731,13 +2737,13 @@
       </c>
       <c r="C63" s="20"/>
       <c r="D63" s="21" t="n">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="E63" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>0.89</v>
+        <v>1.84</v>
       </c>
       <c r="G63" s="23" t="inlineStr">
         <is>
@@ -2745,13 +2751,13 @@
         </is>
       </c>
       <c r="H63" s="39" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="I63" s="40" t="n">
-        <v>0.79</v>
+        <v>0.64</v>
+      </c>
+      <c r="I63" s="25" t="n">
+        <v>1.0</v>
       </c>
       <c r="J63" s="40" t="n">
-        <v>0.1</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="64" customHeight="true" ht="21.75">
@@ -2767,27 +2773,27 @@
         </is>
       </c>
       <c r="D64" s="32" t="n">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="E64" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F64" s="33" t="n">
-        <v>0.89</v>
+        <v>1.84</v>
       </c>
       <c r="G64" s="34" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H64" s="45" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="I64" s="47" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J64" s="46" t="n">
-        <v>0.1</v>
+      <c r="H64" s="46" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I64" s="36" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J64" s="48" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="65" customHeight="true" ht="21.75">
@@ -2799,27 +2805,27 @@
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
       <c r="D65" s="14" t="n">
-        <v>0.0</v>
+        <v>0.64</v>
       </c>
       <c r="E65" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>0.61</v>
+        <v>1.1</v>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H65" s="37" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I65" s="18" t="n">
-        <v>0.0</v>
+        <v>0.8</v>
+      </c>
+      <c r="I65" s="43" t="n">
+        <v>0.2</v>
       </c>
       <c r="J65" s="38" t="n">
-        <v>0.61</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="66" customHeight="true" ht="21.75">
@@ -2835,27 +2841,27 @@
       </c>
       <c r="C66" s="20"/>
       <c r="D66" s="21" t="n">
-        <v>0.0</v>
+        <v>0.64</v>
       </c>
       <c r="E66" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>0.61</v>
+        <v>1.1</v>
       </c>
       <c r="G66" s="23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H66" s="39" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I66" s="25" t="n">
-        <v>0.0</v>
+        <v>0.8</v>
+      </c>
+      <c r="I66" s="44" t="n">
+        <v>0.2</v>
       </c>
       <c r="J66" s="40" t="n">
-        <v>0.61</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="67" customHeight="true" ht="21.75">
@@ -2871,38 +2877,38 @@
         </is>
       </c>
       <c r="D67" s="27" t="n">
-        <v>0.0</v>
+        <v>0.64</v>
       </c>
       <c r="E67" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F67" s="28" t="n">
-        <v>0.61</v>
+        <v>1.1</v>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H67" s="41" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I67" s="31" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J67" s="42" t="n">
-        <v>0.61</v>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="H67" s="49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I67" s="45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J67" s="45" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
-      <c r="D68" s="49" t="n">
+      <c r="D68" s="51" t="n">
         <v>100.0</v>
       </c>
       <c r="E68" s="10"/>
-      <c r="F68" s="49" t="n">
+      <c r="F68" s="51" t="n">
         <v>100.0</v>
       </c>
       <c r="G68" s="10" t="inlineStr">
@@ -2910,14 +2916,14 @@
           <t>100.00</t>
         </is>
       </c>
-      <c r="H68" s="50" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I68" s="49" t="n">
-        <v>99.92</v>
-      </c>
-      <c r="J68" s="49" t="n">
-        <v>0.08</v>
+      <c r="H68" s="52" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I68" s="51" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="J68" s="51" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>

--- a/weeks/undefined_20260929.xlsx
+++ b/weeks/undefined_20260929.xlsx
@@ -505,10 +505,10 @@
     <xf numFmtId="164" fontId="30" fillId="6" borderId="13" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="29" fillId="6" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="24" fillId="8" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="6" borderId="8" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="17" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
@@ -619,13 +619,13 @@
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="H3" s="37" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="I3" s="18" t="n">
         <v>0.0</v>
       </c>
       <c r="J3" s="38" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="4" customHeight="true" ht="21.75">
@@ -655,13 +655,13 @@
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="21" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="H4" s="39" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="I4" s="25" t="n">
         <v>0.0</v>
       </c>
       <c r="J4" s="40" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="5" customHeight="true" ht="21.75">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
@@ -705,13 +705,13 @@
         </is>
       </c>
       <c r="H5" s="41" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="I5" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J5" s="42" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="6" customHeight="true" ht="21.75">
@@ -755,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>20.09</v>
+        <v>20.08</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="H7" s="37" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="I7" s="43" t="n">
         <v>19.2</v>
       </c>
       <c r="J7" s="38" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="21.75">
@@ -1007,7 +1007,7 @@
         <v>0.0</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="H14" s="39" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I14" s="25" t="n">
         <v>0.0</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="15" customHeight="true" ht="21.75">
@@ -1043,7 +1043,7 @@
         <v>0.0</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="H15" s="41" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I15" s="31" t="n">
         <v>0.0</v>
       </c>
       <c r="J15" s="42" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="16" customHeight="true" ht="21.75">
@@ -1111,7 +1111,7 @@
         <v>0.0</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="H17" s="39" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I17" s="44" t="n">
         <v>1.4</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="18" customHeight="true" ht="21.75">
@@ -1147,7 +1147,7 @@
         <v>0.0</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="H18" s="46" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="I18" s="47" t="n">
         <v>1.2</v>
       </c>
       <c r="J18" s="48" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="19" customHeight="true" ht="21.75">
@@ -1327,7 +1327,7 @@
         <v>0.0</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="H23" s="39" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="I23" s="44" t="n">
         <v>0.9</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="21.75">
@@ -1363,7 +1363,7 @@
         <v>0.0</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G24" s="34" t="inlineStr">
         <is>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="H24" s="46" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="I24" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="J24" s="48" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="25" customHeight="true" ht="21.75">
@@ -1389,13 +1389,13 @@
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="14" t="n">
-        <v>7.18</v>
+        <v>6.98</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>7.78</v>
+        <v>7.71</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="H25" s="37" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="I25" s="43" t="n">
         <v>7.7</v>
       </c>
       <c r="J25" s="38" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="26" customHeight="true" ht="21.75">
@@ -1425,13 +1425,13 @@
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" t="n">
-        <v>5.54</v>
+        <v>5.34</v>
       </c>
       <c r="E26" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>5.83</v>
+        <v>5.76</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="H26" s="39" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="I26" s="44" t="n">
         <v>5.8</v>
       </c>
       <c r="J26" s="40" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="27" customHeight="true" ht="21.75">
@@ -1461,13 +1461,13 @@
         </is>
       </c>
       <c r="D27" s="27" t="n">
-        <v>5.54</v>
+        <v>5.34</v>
       </c>
       <c r="E27" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>5.83</v>
+        <v>5.76</v>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="H27" s="41" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="I27" s="45" t="n">
         <v>5.8</v>
       </c>
       <c r="J27" s="42" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="28" customHeight="true" ht="21.75">
@@ -1565,13 +1565,13 @@
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="14" t="n">
-        <v>10.73</v>
+        <v>11.05</v>
       </c>
       <c r="E30" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>12.54</v>
+        <v>12.66</v>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="H30" s="37" t="n">
-        <v>-3.86</v>
+        <v>-3.74</v>
       </c>
       <c r="I30" s="43" t="n">
         <v>17.2</v>
       </c>
       <c r="J30" s="38" t="n">
-        <v>-4.66</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="31" customHeight="true" ht="21.75">
@@ -1607,7 +1607,7 @@
         <v>0.0</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="H31" s="39" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="I31" s="44" t="n">
         <v>3.3</v>
       </c>
       <c r="J31" s="40" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="32" customHeight="true" ht="21.75">
@@ -1643,7 +1643,7 @@
         <v>0.0</v>
       </c>
       <c r="F32" s="33" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="H32" s="46" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="I32" s="47" t="n">
         <v>3.3</v>
       </c>
       <c r="J32" s="48" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="33" customHeight="true" ht="21.75">
@@ -1745,13 +1745,13 @@
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" t="n">
-        <v>5.54</v>
+        <v>5.86</v>
       </c>
       <c r="E35" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>3.86</v>
+        <v>3.97</v>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
@@ -1759,13 +1759,13 @@
         </is>
       </c>
       <c r="H35" s="39" t="n">
-        <v>-1.74</v>
+        <v>-1.63</v>
       </c>
       <c r="I35" s="44" t="n">
         <v>5.8</v>
       </c>
       <c r="J35" s="40" t="n">
-        <v>-1.94</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="36" customHeight="true" ht="21.75">
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="D36" s="32" t="n">
-        <v>5.54</v>
+        <v>5.86</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F36" s="33" t="n">
-        <v>3.86</v>
+        <v>3.97</v>
       </c>
       <c r="G36" s="34" t="inlineStr">
         <is>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="H36" s="46" t="n">
-        <v>-1.74</v>
+        <v>-1.63</v>
       </c>
       <c r="I36" s="47" t="n">
         <v>5.8</v>
       </c>
       <c r="J36" s="48" t="n">
-        <v>-1.94</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="37" customHeight="true" ht="21.75">
@@ -1813,13 +1813,13 @@
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="14" t="n">
-        <v>16.42</v>
+        <v>16.62</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>14.7</v>
+        <v>14.78</v>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="H37" s="37" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="I37" s="43" t="n">
         <v>14.2</v>
       </c>
       <c r="J37" s="38" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="38" customHeight="true" ht="21.75">
@@ -1921,13 +1921,13 @@
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" t="n">
-        <v>5.27</v>
+        <v>5.47</v>
       </c>
       <c r="E40" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
@@ -1935,13 +1935,13 @@
         </is>
       </c>
       <c r="H40" s="39" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="I40" s="44" t="n">
         <v>5.3</v>
       </c>
       <c r="J40" s="40" t="n">
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="41" customHeight="true" ht="21.75">
@@ -1957,27 +1957,27 @@
         </is>
       </c>
       <c r="D41" s="27" t="n">
-        <v>5.27</v>
+        <v>5.47</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H41" s="49" t="n">
-        <v>0.3</v>
+      <c r="H41" s="41" t="n">
+        <v>0.38</v>
       </c>
       <c r="I41" s="45" t="n">
         <v>5.3</v>
       </c>
-      <c r="J41" s="31" t="n">
-        <v>0.0</v>
+      <c r="J41" s="42" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="42" customHeight="true" ht="21.75">
@@ -2218,7 +2218,7 @@
           <t>4.7</t>
         </is>
       </c>
-      <c r="H48" s="50" t="n">
+      <c r="H48" s="49" t="n">
         <v>-1.4</v>
       </c>
       <c r="I48" s="47" t="n">
@@ -2345,13 +2345,13 @@
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="14" t="n">
-        <v>15.05</v>
+        <v>14.97</v>
       </c>
       <c r="E52" s="14" t="n">
         <v>0.0</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>16.6</v>
+        <v>16.57</v>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
@@ -2359,13 +2359,13 @@
         </is>
       </c>
       <c r="H52" s="37" t="n">
-        <v>-2.5</v>
+        <v>-2.53</v>
       </c>
       <c r="I52" s="43" t="n">
         <v>20.3</v>
       </c>
       <c r="J52" s="38" t="n">
-        <v>-3.7</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="53" customHeight="true" ht="21.75">
@@ -2453,13 +2453,13 @@
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="21" t="n">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="E55" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>7.13</v>
+        <v>7.1</v>
       </c>
       <c r="G55" s="23" t="inlineStr">
         <is>
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="H55" s="39" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="I55" s="44" t="n">
         <v>7.7</v>
       </c>
       <c r="J55" s="40" t="n">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="56" customHeight="true" ht="21.75">
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="D56" s="32" t="n">
-        <v>5.44</v>
+        <v>5.36</v>
       </c>
       <c r="E56" s="32" t="n">
         <v>0.0</v>
       </c>
       <c r="F56" s="33" t="n">
-        <v>6.29</v>
+        <v>6.26</v>
       </c>
       <c r="G56" s="34" t="inlineStr">
         <is>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="H56" s="46" t="n">
-        <v>-1.11</v>
+        <v>-1.14</v>
       </c>
       <c r="I56" s="47" t="n">
         <v>7.7</v>
       </c>
       <c r="J56" s="48" t="n">
-        <v>-1.41</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="57" customHeight="true" ht="21.75">
@@ -2561,13 +2561,13 @@
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="21" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="E58" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F58" s="22" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="H58" s="39" t="n">
-        <v>-0.56</v>
+        <v>-0.62</v>
       </c>
       <c r="I58" s="44" t="n">
         <v>4.3</v>
       </c>
       <c r="J58" s="40" t="n">
-        <v>-0.86</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="59" customHeight="true" ht="21.75">
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="D59" s="27" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="E59" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
@@ -2611,13 +2611,13 @@
         </is>
       </c>
       <c r="H59" s="41" t="n">
-        <v>-0.56</v>
+        <v>-0.62</v>
       </c>
       <c r="I59" s="45" t="n">
         <v>4.3</v>
       </c>
       <c r="J59" s="42" t="n">
-        <v>-0.86</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="21.75">
@@ -2633,13 +2633,13 @@
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="21" t="n">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="E60" s="21" t="n">
         <v>0.0</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="H60" s="39" t="n">
-        <v>-0.55</v>
+        <v>-0.49</v>
       </c>
       <c r="I60" s="44" t="n">
         <v>3.6</v>
       </c>
       <c r="J60" s="40" t="n">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="61" customHeight="true" ht="21.75">
@@ -2669,13 +2669,13 @@
         </is>
       </c>
       <c r="D61" s="27" t="n">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="E61" s="27" t="n">
         <v>0.0</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="H61" s="41" t="n">
-        <v>-0.55</v>
+        <v>-0.49</v>
       </c>
       <c r="I61" s="45" t="n">
         <v>3.6</v>
       </c>
       <c r="J61" s="42" t="n">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="62" customHeight="true" ht="21.75">
@@ -2890,7 +2890,7 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="H67" s="49" t="n">
+      <c r="H67" s="50" t="n">
         <v>0.8</v>
       </c>
       <c r="I67" s="45" t="n">
